--- a/AAII_Financials/Quarterly/AFBI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AFBI_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Quarterly/AFBI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AFBI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="92">
   <si>
     <t>AFBI</t>
   </si>
@@ -656,107 +656,114 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -764,64 +771,70 @@
         <v>10800</v>
       </c>
       <c r="E8" s="3">
+        <v>10800</v>
+      </c>
+      <c r="F8" s="3">
+        <v>10800</v>
+      </c>
+      <c r="G8" s="3">
         <v>10500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>9200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>9000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>8200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>7600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>8300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>7400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>7600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>8200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>9200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>8000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>8700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>7300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>6700</v>
-      </c>
-      <c r="S8" s="3">
-        <v>3800</v>
-      </c>
-      <c r="T8" s="3">
-        <v>3900</v>
       </c>
       <c r="U8" s="3">
         <v>3800</v>
       </c>
       <c r="V8" s="3">
+        <v>3900</v>
+      </c>
+      <c r="W8" s="3">
+        <v>3800</v>
+      </c>
+      <c r="X8" s="3">
         <v>3600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>3600</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -885,8 +898,14 @@
       <c r="W9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -950,8 +969,14 @@
       <c r="W10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -975,8 +1000,10 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1040,8 +1067,14 @@
       <c r="W12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1105,8 +1138,14 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1170,8 +1209,14 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1235,8 +1280,14 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1257,43 +1308,45 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>4000</v>
+      </c>
+      <c r="F17" s="3">
         <v>3900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>3800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>2300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>1700</v>
-      </c>
-      <c r="H17" s="3">
-        <v>800</v>
-      </c>
-      <c r="I17" s="3">
-        <v>700</v>
       </c>
       <c r="J17" s="3">
         <v>800</v>
       </c>
       <c r="K17" s="3">
+        <v>700</v>
+      </c>
+      <c r="L17" s="3">
         <v>800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
+        <v>800</v>
+      </c>
+      <c r="N17" s="3">
         <v>1000</v>
-      </c>
-      <c r="M17" s="3">
-        <v>1100</v>
-      </c>
-      <c r="N17" s="3">
-        <v>1400</v>
       </c>
       <c r="O17" s="3">
         <v>1100</v>
@@ -1302,93 +1355,105 @@
         <v>1400</v>
       </c>
       <c r="Q17" s="3">
+        <v>1100</v>
+      </c>
+      <c r="R17" s="3">
+        <v>1400</v>
+      </c>
+      <c r="S17" s="3">
         <v>1500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>1500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>600</v>
-      </c>
-      <c r="U17" s="3">
-        <v>500</v>
-      </c>
-      <c r="V17" s="3">
-        <v>500</v>
       </c>
       <c r="W17" s="3">
         <v>500</v>
       </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X17" s="3">
+        <v>500</v>
+      </c>
+      <c r="Y17" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>6900</v>
+        <v>6800</v>
       </c>
       <c r="E18" s="3">
-        <v>6700</v>
+        <v>6800</v>
       </c>
       <c r="F18" s="3">
         <v>6900</v>
       </c>
       <c r="G18" s="3">
+        <v>6700</v>
+      </c>
+      <c r="H18" s="3">
+        <v>6900</v>
+      </c>
+      <c r="I18" s="3">
         <v>7300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>7400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>6900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>7500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>6600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>6600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>7100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>7800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>6900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>7300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>5800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>5200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>3100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>3300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>3300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>3100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1412,91 +1477,99 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-4800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="G20" s="3">
         <v>-4600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-4600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-5100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-4900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-4600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-5200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-4800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-4200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-4100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-5100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-5000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-4800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-4400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-7100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-2800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-3600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-3100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-3000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-2900</v>
       </c>
     </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E21" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F21" s="3">
         <v>2300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>2300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>2400</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I21" s="3" t="s">
         <v>5</v>
       </c>
@@ -1512,38 +1585,44 @@
       <c r="M21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P21" s="3">
         <v>2900</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>5</v>
       </c>
       <c r="R21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U21" s="3">
         <v>600</v>
       </c>
-      <c r="T21" s="3">
-        <v>0</v>
-      </c>
-      <c r="U21" s="3">
-        <v>300</v>
-      </c>
       <c r="V21" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="W21" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3">
+        <v>300</v>
+      </c>
+      <c r="Y21" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1607,81 +1686,93 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E23" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F23" s="3">
         <v>2100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>2100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>2200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>2200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>2400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>2300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>2300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>1800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>2400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>3000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>2700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>1900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>2400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>1400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-1800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="E24" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="F24" s="3">
         <v>500</v>
@@ -1690,55 +1781,61 @@
         <v>500</v>
       </c>
       <c r="H24" s="3">
+        <v>500</v>
+      </c>
+      <c r="I24" s="3">
+        <v>500</v>
+      </c>
+      <c r="J24" s="3">
         <v>600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>400</v>
-      </c>
-      <c r="L24" s="3">
-        <v>600</v>
-      </c>
-      <c r="M24" s="3">
-        <v>700</v>
       </c>
       <c r="N24" s="3">
         <v>600</v>
       </c>
       <c r="O24" s="3">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="P24" s="3">
         <v>600</v>
       </c>
       <c r="Q24" s="3">
+        <v>500</v>
+      </c>
+      <c r="R24" s="3">
+        <v>600</v>
+      </c>
+      <c r="S24" s="3">
         <v>300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>-500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>-100</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
-      <c r="V24" s="3">
-        <v>0</v>
-      </c>
       <c r="W24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1802,138 +1899,156 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E26" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F26" s="3">
         <v>1600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>1600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>1700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>1700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>1900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>1800</v>
-      </c>
-      <c r="J26" s="3">
-        <v>1800</v>
-      </c>
-      <c r="K26" s="3">
-        <v>1300</v>
       </c>
       <c r="L26" s="3">
         <v>1800</v>
       </c>
       <c r="M26" s="3">
+        <v>1300</v>
+      </c>
+      <c r="N26" s="3">
+        <v>1800</v>
+      </c>
+      <c r="O26" s="3">
         <v>2300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>2100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>1400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>1900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>1100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-1300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-200</v>
-      </c>
-      <c r="U26" s="3">
-        <v>100</v>
-      </c>
-      <c r="V26" s="3">
-        <v>100</v>
       </c>
       <c r="W26" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X26" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y26" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E27" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F27" s="3">
         <v>1600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>1600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>1700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>1700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>1900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>1800</v>
-      </c>
-      <c r="J27" s="3">
-        <v>1800</v>
-      </c>
-      <c r="K27" s="3">
-        <v>1300</v>
       </c>
       <c r="L27" s="3">
         <v>1800</v>
       </c>
       <c r="M27" s="3">
+        <v>1300</v>
+      </c>
+      <c r="N27" s="3">
+        <v>1800</v>
+      </c>
+      <c r="O27" s="3">
         <v>2300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>2100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>1400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>1900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>1100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-1300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-200</v>
-      </c>
-      <c r="U27" s="3">
-        <v>100</v>
-      </c>
-      <c r="V27" s="3">
-        <v>100</v>
       </c>
       <c r="W27" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X27" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y27" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1997,8 +2112,14 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2044,11 +2165,11 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S29" s="3" t="s">
-        <v>5</v>
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3">
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>5</v>
@@ -2062,8 +2183,14 @@
       <c r="W29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2127,8 +2254,14 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2192,138 +2325,156 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E32" s="3">
         <v>4800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
+        <v>4800</v>
+      </c>
+      <c r="G32" s="3">
         <v>4600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>4600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>5100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>4900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>4600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>5200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>4800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>4200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>4100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>5100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>5000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>4800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>4400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>7100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>2800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>3600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>3100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>3000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E33" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F33" s="3">
         <v>1600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>1600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>1700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>1700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>1900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>1800</v>
-      </c>
-      <c r="J33" s="3">
-        <v>1800</v>
-      </c>
-      <c r="K33" s="3">
-        <v>1300</v>
       </c>
       <c r="L33" s="3">
         <v>1800</v>
       </c>
       <c r="M33" s="3">
+        <v>1300</v>
+      </c>
+      <c r="N33" s="3">
+        <v>1800</v>
+      </c>
+      <c r="O33" s="3">
         <v>2300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>2100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>1400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>1900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>1100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-1300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-200</v>
-      </c>
-      <c r="U33" s="3">
-        <v>100</v>
-      </c>
-      <c r="V33" s="3">
-        <v>100</v>
       </c>
       <c r="W33" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X33" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y33" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2387,143 +2538,161 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E35" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F35" s="3">
         <v>1600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>1600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>1700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>1700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>1900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>1800</v>
-      </c>
-      <c r="J35" s="3">
-        <v>1800</v>
-      </c>
-      <c r="K35" s="3">
-        <v>1300</v>
       </c>
       <c r="L35" s="3">
         <v>1800</v>
       </c>
       <c r="M35" s="3">
+        <v>1300</v>
+      </c>
+      <c r="N35" s="3">
+        <v>1800</v>
+      </c>
+      <c r="O35" s="3">
         <v>2300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>2100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>1400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>1900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>1100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-1300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-200</v>
-      </c>
-      <c r="U35" s="3">
-        <v>100</v>
-      </c>
-      <c r="V35" s="3">
-        <v>100</v>
       </c>
       <c r="W35" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X35" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y35" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2547,8 +2716,10 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2572,73 +2743,81 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E41" s="3">
+        <v>6000</v>
+      </c>
+      <c r="F41" s="3">
         <v>5400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>7100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>5700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>2900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>6900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>8100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>14300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>16200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>17300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>15300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>10000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>5600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>6200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>14300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>6400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>4000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>3300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>4600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>4600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2646,64 +2825,70 @@
         <v>77700</v>
       </c>
       <c r="E42" s="3">
+        <v>66300</v>
+      </c>
+      <c r="F42" s="3">
+        <v>77700</v>
+      </c>
+      <c r="G42" s="3">
         <v>94000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>151500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>37000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>43900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>57700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>66100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>107300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>122700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>109000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>97600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>176900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>178200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>185600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>47200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>44400</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>35000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>15400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>26300</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>33800</v>
       </c>
     </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2767,8 +2952,14 @@
       <c r="W43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2832,8 +3023,14 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2897,8 +3094,14 @@
       <c r="W45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2962,8 +3165,14 @@
       <c r="W46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3027,127 +3236,139 @@
       <c r="W47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E48" s="3">
+        <v>3800</v>
+      </c>
+      <c r="F48" s="3">
         <v>3900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>4100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>4200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>4300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>4100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>4000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>4000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>3800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>7400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>7500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>7600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>8600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>8800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>8900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>9500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>8500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>8600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>8800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>8800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>8900</v>
       </c>
     </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>18300</v>
+      </c>
+      <c r="E49" s="3">
         <v>18400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
+        <v>18400</v>
+      </c>
+      <c r="G49" s="3">
         <v>18500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>18500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>18600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>18600</v>
-      </c>
-      <c r="I49" s="3">
-        <v>18700</v>
-      </c>
-      <c r="J49" s="3">
-        <v>18700</v>
       </c>
       <c r="K49" s="3">
         <v>18700</v>
       </c>
       <c r="L49" s="3">
+        <v>18700</v>
+      </c>
+      <c r="M49" s="3">
+        <v>18700</v>
+      </c>
+      <c r="N49" s="3">
         <v>18800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>18800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>18900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>18900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>19000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>19000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>19100</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U49" s="3" t="s">
         <v>5</v>
       </c>
@@ -3157,8 +3378,14 @@
       <c r="W49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3222,8 +3449,14 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3287,8 +3520,14 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3352,8 +3591,14 @@
       <c r="W52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3417,73 +3662,85 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>869500</v>
+      </c>
+      <c r="E54" s="3">
+        <v>843300</v>
+      </c>
+      <c r="F54" s="3">
         <v>855400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>876900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>932300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>791300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>776400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>766700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>760200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>788100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>790000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>786800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>797300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>850600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>888200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>906400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>642800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>319300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>309700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>305100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>308000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>307700</v>
       </c>
     </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3507,8 +3764,10 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3532,73 +3791,81 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>7300</v>
+      </c>
+      <c r="F57" s="3">
         <v>7900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>7900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>8200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>7000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>5200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>5100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>5800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>3300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>6000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>8200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>7800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>4700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>7600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>5300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>4600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>3900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>4100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>5300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>4700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>4500</v>
       </c>
     </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3662,8 +3929,14 @@
       <c r="W58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3727,8 +4000,14 @@
       <c r="W59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3792,8 +4071,14 @@
       <c r="W60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3831,20 +4116,20 @@
         <v>0</v>
       </c>
       <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
         <v>105800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>130000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>129200</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -3857,8 +4142,14 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3922,8 +4213,14 @@
       <c r="W62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3987,8 +4284,14 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4052,8 +4355,14 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4117,73 +4426,85 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>746200</v>
+      </c>
+      <c r="E66" s="3">
+        <v>721700</v>
+      </c>
+      <c r="F66" s="3">
         <v>737000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>759000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>814000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>674200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>661200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>651300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>643900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>667100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>670300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>669200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>682000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>769800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>809000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>829100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>566900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>242100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>233200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>228300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>231700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>231300</v>
       </c>
     </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4207,8 +4528,10 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4272,8 +4595,14 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4337,8 +4666,14 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4402,8 +4737,14 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4467,73 +4808,85 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>72700</v>
+      </c>
+      <c r="E72" s="3">
+        <v>71300</v>
+      </c>
+      <c r="F72" s="3">
         <v>69800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>68200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>66600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>65400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>63700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>61800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>60000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>58200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>56900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>55100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>52800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>50700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>49200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>47300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>46300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>47600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>47100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>47300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>47200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>47000</v>
       </c>
     </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4597,8 +4950,14 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4662,8 +5021,14 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4727,73 +5092,85 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>123300</v>
+      </c>
+      <c r="E76" s="3">
+        <v>121500</v>
+      </c>
+      <c r="F76" s="3">
         <v>118500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>117900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>118300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>117100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>115200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>115400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>116400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>121000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>119700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>117600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>115300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>80800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>79200</v>
-      </c>
-      <c r="Q76" s="3">
-        <v>77200</v>
-      </c>
-      <c r="R76" s="3">
-        <v>75900</v>
       </c>
       <c r="S76" s="3">
         <v>77200</v>
       </c>
       <c r="T76" s="3">
+        <v>75900</v>
+      </c>
+      <c r="U76" s="3">
+        <v>77200</v>
+      </c>
+      <c r="V76" s="3">
         <v>76500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>76800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>76300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>76400</v>
       </c>
     </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4857,143 +5234,161 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E81" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F81" s="3">
         <v>1600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>1600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>1700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>1700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>1900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>1800</v>
-      </c>
-      <c r="J81" s="3">
-        <v>1800</v>
-      </c>
-      <c r="K81" s="3">
-        <v>1300</v>
       </c>
       <c r="L81" s="3">
         <v>1800</v>
       </c>
       <c r="M81" s="3">
+        <v>1300</v>
+      </c>
+      <c r="N81" s="3">
+        <v>1800</v>
+      </c>
+      <c r="O81" s="3">
         <v>2300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>2100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>1400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>1900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>1100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-1300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-200</v>
-      </c>
-      <c r="U81" s="3">
-        <v>100</v>
-      </c>
-      <c r="V81" s="3">
-        <v>100</v>
       </c>
       <c r="W81" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X81" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y81" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5017,8 +5412,10 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5031,11 +5428,11 @@
       <c r="F83" s="3">
         <v>200</v>
       </c>
-      <c r="G83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>5</v>
+      <c r="G83" s="3">
+        <v>200</v>
+      </c>
+      <c r="H83" s="3">
+        <v>200</v>
       </c>
       <c r="I83" s="3" t="s">
         <v>5</v>
@@ -5046,44 +5443,50 @@
       <c r="K83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
+      <c r="L83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M83" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N83" s="3">
+        <v>0</v>
+      </c>
+      <c r="O83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P83" s="3">
         <v>200</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q83" s="3" t="s">
         <v>5</v>
       </c>
       <c r="R83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S83" s="3">
-        <v>200</v>
-      </c>
-      <c r="T83" s="3">
-        <v>300</v>
+      <c r="S83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="U83" s="3">
         <v>200</v>
       </c>
       <c r="V83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="W83" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y83" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5147,8 +5550,14 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5212,8 +5621,14 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5277,8 +5692,14 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5342,8 +5763,14 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5407,73 +5834,85 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E89" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F89" s="3">
         <v>1700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>2300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>2000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>2400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>2000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>3900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-1300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>3800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>8700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>1800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>2400</v>
       </c>
-      <c r="Q89" s="3">
-        <v>0</v>
-      </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
+        <v>0</v>
+      </c>
+      <c r="T89" s="3">
         <v>-2900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>1000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5497,8 +5936,10 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5506,64 +5947,70 @@
         <v>-100</v>
       </c>
       <c r="E91" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="F91" s="3">
         <v>-100</v>
       </c>
       <c r="G91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I91" s="3">
         <v>-500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-300</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-300</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-400</v>
       </c>
       <c r="K91" s="3">
         <v>-300</v>
       </c>
       <c r="L91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="M91" s="3">
         <v>-300</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-300</v>
-      </c>
-      <c r="P91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>0</v>
       </c>
       <c r="R91" s="3">
         <v>-100</v>
       </c>
       <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
         <v>-100</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
       <c r="U91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3">
         <v>-200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-100</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5627,8 +6074,14 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5692,73 +6145,85 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-14700</v>
+      </c>
+      <c r="E94" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F94" s="3">
         <v>-800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-29200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-26300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-26600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-23800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-17100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-17400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>11200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>23700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-27100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>33400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>5100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-115600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-33300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>13000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-7500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-7000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-4800</v>
       </c>
     </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5782,8 +6247,10 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5847,8 +6314,14 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5912,8 +6385,14 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5977,8 +6456,14 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6042,73 +6527,85 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>24800</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-14900</v>
+      </c>
+      <c r="F100" s="3">
         <v>-22300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-56600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>137800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>12800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>9300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>7300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-28700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>3300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-13200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-58400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-36600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-22300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>261700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>36400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>9100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>6000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-3900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6172,69 +6669,81 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>11400</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-11500</v>
+      </c>
+      <c r="F102" s="3">
         <v>-21400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-54000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>110600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-14200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-14900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-14500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-41900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-19100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>15200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>14300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-76900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-1300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-14900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>146100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>10100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>18300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-11000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-6400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-3800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AFBI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AFBI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="92">
   <si>
     <t>AFBI</t>
   </si>
@@ -656,119 +656,123 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>10800</v>
+        <v>11700</v>
       </c>
       <c r="E8" s="3">
         <v>10800</v>
@@ -777,64 +781,67 @@
         <v>10800</v>
       </c>
       <c r="G8" s="3">
+        <v>10800</v>
+      </c>
+      <c r="H8" s="3">
         <v>10500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>9200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>9000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>8200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>7600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>8300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>7400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>7600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>8200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>9200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>8000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>8700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>7300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>6700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3800</v>
-      </c>
-      <c r="X8" s="3">
-        <v>3600</v>
       </c>
       <c r="Y8" s="3">
         <v>3600</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3">
+        <v>3600</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -904,8 +911,11 @@
       <c r="Y9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -975,8 +985,11 @@
       <c r="Y10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1002,8 +1015,9 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1073,8 +1087,11 @@
       <c r="Y12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1144,8 +1161,11 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1215,8 +1235,11 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1286,8 +1309,11 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1310,70 +1336,71 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>4000</v>
+        <v>4300</v>
       </c>
       <c r="E17" s="3">
         <v>4000</v>
       </c>
       <c r="F17" s="3">
+        <v>4000</v>
+      </c>
+      <c r="G17" s="3">
         <v>3900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>700</v>
-      </c>
-      <c r="L17" s="3">
-        <v>800</v>
       </c>
       <c r="M17" s="3">
         <v>800</v>
       </c>
       <c r="N17" s="3">
+        <v>800</v>
+      </c>
+      <c r="O17" s="3">
         <v>1000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1400</v>
-      </c>
-      <c r="S17" s="3">
-        <v>1500</v>
       </c>
       <c r="T17" s="3">
         <v>1500</v>
       </c>
       <c r="U17" s="3">
+        <v>1500</v>
+      </c>
+      <c r="V17" s="3">
         <v>700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>600</v>
-      </c>
-      <c r="W17" s="3">
-        <v>500</v>
       </c>
       <c r="X17" s="3">
         <v>500</v>
@@ -1381,79 +1408,85 @@
       <c r="Y17" s="3">
         <v>500</v>
       </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>6800</v>
+        <v>7400</v>
       </c>
       <c r="E18" s="3">
         <v>6800</v>
       </c>
       <c r="F18" s="3">
+        <v>6800</v>
+      </c>
+      <c r="G18" s="3">
         <v>6900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>6700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>6900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>7300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>7400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>6900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>7500</v>
-      </c>
-      <c r="M18" s="3">
-        <v>6600</v>
       </c>
       <c r="N18" s="3">
         <v>6600</v>
       </c>
       <c r="O18" s="3">
+        <v>6600</v>
+      </c>
+      <c r="P18" s="3">
         <v>7100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>7800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>6900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>7300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>5800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>5200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>3100</v>
-      </c>
-      <c r="V18" s="3">
-        <v>3300</v>
       </c>
       <c r="W18" s="3">
         <v>3300</v>
       </c>
       <c r="X18" s="3">
-        <v>3100</v>
+        <v>3300</v>
       </c>
       <c r="Y18" s="3">
         <v>3100</v>
       </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3">
+        <v>3100</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1479,100 +1512,104 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-5000</v>
-      </c>
-      <c r="E20" s="3">
-        <v>-4800</v>
       </c>
       <c r="F20" s="3">
         <v>-4800</v>
       </c>
       <c r="G20" s="3">
-        <v>-4600</v>
+        <v>-4800</v>
       </c>
       <c r="H20" s="3">
         <v>-4600</v>
       </c>
       <c r="I20" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="J20" s="3">
         <v>-5100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-4900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-4600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-5200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-4800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-4200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-4100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-5000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-4800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-4400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-7100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-2800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-3600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-3100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-3000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-2900</v>
       </c>
     </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E21" s="3">
         <v>1900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2100</v>
-      </c>
-      <c r="F21" s="3">
-        <v>2300</v>
       </c>
       <c r="G21" s="3">
         <v>2300</v>
       </c>
       <c r="H21" s="3">
+        <v>2300</v>
+      </c>
+      <c r="I21" s="3">
         <v>2400</v>
       </c>
-      <c r="I21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J21" s="3" t="s">
         <v>5</v>
       </c>
@@ -1591,12 +1628,12 @@
       <c r="O21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q21" s="3">
         <v>2900</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>5</v>
       </c>
@@ -1606,14 +1643,14 @@
       <c r="T21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V21" s="3">
         <v>600</v>
       </c>
-      <c r="V21" s="3">
-        <v>0</v>
-      </c>
       <c r="W21" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="X21" s="3">
         <v>300</v>
@@ -1621,8 +1658,11 @@
       <c r="Y21" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1692,90 +1732,96 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E23" s="3">
         <v>1800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1900</v>
-      </c>
-      <c r="F23" s="3">
-        <v>2100</v>
       </c>
       <c r="G23" s="3">
         <v>2100</v>
       </c>
       <c r="H23" s="3">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="I23" s="3">
         <v>2200</v>
       </c>
       <c r="J23" s="3">
+        <v>2200</v>
+      </c>
+      <c r="K23" s="3">
         <v>2400</v>
-      </c>
-      <c r="K23" s="3">
-        <v>2300</v>
       </c>
       <c r="L23" s="3">
         <v>2300</v>
       </c>
       <c r="M23" s="3">
+        <v>2300</v>
+      </c>
+      <c r="N23" s="3">
         <v>1800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>3000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-1800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-300</v>
-      </c>
-      <c r="W23" s="3">
-        <v>100</v>
       </c>
       <c r="X23" s="3">
         <v>100</v>
       </c>
       <c r="Y23" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z23" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E24" s="3">
         <v>400</v>
       </c>
       <c r="F24" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="G24" s="3">
         <v>500</v>
@@ -1787,55 +1833,58 @@
         <v>500</v>
       </c>
       <c r="J24" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="K24" s="3">
         <v>600</v>
       </c>
       <c r="L24" s="3">
+        <v>600</v>
+      </c>
+      <c r="M24" s="3">
         <v>500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-100</v>
       </c>
-      <c r="W24" s="3">
-        <v>0</v>
-      </c>
       <c r="X24" s="3">
         <v>0</v>
       </c>
       <c r="Y24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1905,70 +1954,73 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1500</v>
-      </c>
-      <c r="F26" s="3">
-        <v>1600</v>
       </c>
       <c r="G26" s="3">
         <v>1600</v>
       </c>
       <c r="H26" s="3">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="I26" s="3">
         <v>1700</v>
       </c>
       <c r="J26" s="3">
+        <v>1700</v>
+      </c>
+      <c r="K26" s="3">
         <v>1900</v>
-      </c>
-      <c r="K26" s="3">
-        <v>1800</v>
       </c>
       <c r="L26" s="3">
         <v>1800</v>
       </c>
       <c r="M26" s="3">
+        <v>1800</v>
+      </c>
+      <c r="N26" s="3">
         <v>1300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-1300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-200</v>
-      </c>
-      <c r="W26" s="3">
-        <v>100</v>
       </c>
       <c r="X26" s="3">
         <v>100</v>
@@ -1976,70 +2028,73 @@
       <c r="Y26" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1500</v>
-      </c>
-      <c r="F27" s="3">
-        <v>1600</v>
       </c>
       <c r="G27" s="3">
         <v>1600</v>
       </c>
       <c r="H27" s="3">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="I27" s="3">
         <v>1700</v>
       </c>
       <c r="J27" s="3">
+        <v>1700</v>
+      </c>
+      <c r="K27" s="3">
         <v>1900</v>
-      </c>
-      <c r="K27" s="3">
-        <v>1800</v>
       </c>
       <c r="L27" s="3">
         <v>1800</v>
       </c>
       <c r="M27" s="3">
+        <v>1800</v>
+      </c>
+      <c r="N27" s="3">
         <v>1300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-1300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-200</v>
-      </c>
-      <c r="W27" s="3">
-        <v>100</v>
       </c>
       <c r="X27" s="3">
         <v>100</v>
@@ -2047,8 +2102,11 @@
       <c r="Y27" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2118,8 +2176,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2171,8 +2232,8 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>5</v>
+      <c r="T29" s="3">
+        <v>0</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>5</v>
@@ -2189,8 +2250,11 @@
       <c r="Y29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2260,8 +2324,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2331,141 +2398,147 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E32" s="3">
         <v>5000</v>
-      </c>
-      <c r="E32" s="3">
-        <v>4800</v>
       </c>
       <c r="F32" s="3">
         <v>4800</v>
       </c>
       <c r="G32" s="3">
-        <v>4600</v>
+        <v>4800</v>
       </c>
       <c r="H32" s="3">
         <v>4600</v>
       </c>
       <c r="I32" s="3">
+        <v>4600</v>
+      </c>
+      <c r="J32" s="3">
         <v>5100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>4900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>4600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>5200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>4800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>4200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>4100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>5100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>5000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>4800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>4400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>7100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>2800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>3600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>3100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>3000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1500</v>
-      </c>
-      <c r="F33" s="3">
-        <v>1600</v>
       </c>
       <c r="G33" s="3">
         <v>1600</v>
       </c>
       <c r="H33" s="3">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="I33" s="3">
         <v>1700</v>
       </c>
       <c r="J33" s="3">
+        <v>1700</v>
+      </c>
+      <c r="K33" s="3">
         <v>1900</v>
-      </c>
-      <c r="K33" s="3">
-        <v>1800</v>
       </c>
       <c r="L33" s="3">
         <v>1800</v>
       </c>
       <c r="M33" s="3">
+        <v>1800</v>
+      </c>
+      <c r="N33" s="3">
         <v>1300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-1300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-200</v>
-      </c>
-      <c r="W33" s="3">
-        <v>100</v>
       </c>
       <c r="X33" s="3">
         <v>100</v>
@@ -2473,8 +2546,11 @@
       <c r="Y33" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2544,70 +2620,73 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1500</v>
-      </c>
-      <c r="F35" s="3">
-        <v>1600</v>
       </c>
       <c r="G35" s="3">
         <v>1600</v>
       </c>
       <c r="H35" s="3">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="I35" s="3">
         <v>1700</v>
       </c>
       <c r="J35" s="3">
+        <v>1700</v>
+      </c>
+      <c r="K35" s="3">
         <v>1900</v>
-      </c>
-      <c r="K35" s="3">
-        <v>1800</v>
       </c>
       <c r="L35" s="3">
         <v>1800</v>
       </c>
       <c r="M35" s="3">
+        <v>1800</v>
+      </c>
+      <c r="N35" s="3">
         <v>1300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-1300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-200</v>
-      </c>
-      <c r="W35" s="3">
-        <v>100</v>
       </c>
       <c r="X35" s="3">
         <v>100</v>
@@ -2615,84 +2694,90 @@
       <c r="Y35" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2718,8 +2803,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2745,150 +2831,157 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E41" s="3">
         <v>6400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>5400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>7100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>5700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>8100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>14300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>16200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>17300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>15300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>10000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>5600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>6200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>14300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>6400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>4000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>3300</v>
-      </c>
-      <c r="W41" s="3">
-        <v>4600</v>
       </c>
       <c r="X41" s="3">
         <v>4600</v>
       </c>
       <c r="Y41" s="3">
+        <v>4600</v>
+      </c>
+      <c r="Z41" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>66200</v>
+      </c>
+      <c r="E42" s="3">
         <v>77700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>66300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>77700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>94000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>151500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>37000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>43900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>57700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>66100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>107300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>122700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>109000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>97600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>176900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>178200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>185600</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>47200</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>44400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>35000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>15400</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>26300</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>33800</v>
       </c>
     </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2958,8 +3051,11 @@
       <c r="Y43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3029,8 +3125,11 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3100,8 +3199,11 @@
       <c r="Y45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3171,8 +3273,11 @@
       <c r="Y46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3242,79 +3347,85 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E48" s="3">
         <v>3700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4100</v>
-      </c>
-      <c r="K48" s="3">
-        <v>4000</v>
       </c>
       <c r="L48" s="3">
         <v>4000</v>
       </c>
       <c r="M48" s="3">
+        <v>4000</v>
+      </c>
+      <c r="N48" s="3">
         <v>3800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>7400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>7500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>7600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>8600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>8800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>8900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>9500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>8500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>8600</v>
-      </c>
-      <c r="W48" s="3">
-        <v>8800</v>
       </c>
       <c r="X48" s="3">
         <v>8800</v>
       </c>
       <c r="Y48" s="3">
+        <v>8800</v>
+      </c>
+      <c r="Z48" s="3">
         <v>8900</v>
       </c>
     </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3322,25 +3433,25 @@
         <v>18300</v>
       </c>
       <c r="E49" s="3">
-        <v>18400</v>
+        <v>18300</v>
       </c>
       <c r="F49" s="3">
         <v>18400</v>
       </c>
       <c r="G49" s="3">
-        <v>18500</v>
+        <v>18400</v>
       </c>
       <c r="H49" s="3">
         <v>18500</v>
       </c>
       <c r="I49" s="3">
-        <v>18600</v>
+        <v>18500</v>
       </c>
       <c r="J49" s="3">
         <v>18600</v>
       </c>
       <c r="K49" s="3">
-        <v>18700</v>
+        <v>18600</v>
       </c>
       <c r="L49" s="3">
         <v>18700</v>
@@ -3349,29 +3460,29 @@
         <v>18700</v>
       </c>
       <c r="N49" s="3">
-        <v>18800</v>
+        <v>18700</v>
       </c>
       <c r="O49" s="3">
         <v>18800</v>
       </c>
       <c r="P49" s="3">
-        <v>18900</v>
+        <v>18800</v>
       </c>
       <c r="Q49" s="3">
         <v>18900</v>
       </c>
       <c r="R49" s="3">
-        <v>19000</v>
+        <v>18900</v>
       </c>
       <c r="S49" s="3">
         <v>19000</v>
       </c>
       <c r="T49" s="3">
+        <v>19000</v>
+      </c>
+      <c r="U49" s="3">
         <v>19100</v>
       </c>
-      <c r="U49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V49" s="3" t="s">
         <v>5</v>
       </c>
@@ -3384,8 +3495,11 @@
       <c r="Y49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3455,8 +3569,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3526,8 +3643,11 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3597,8 +3717,11 @@
       <c r="Y52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3668,79 +3791,85 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>873600</v>
+      </c>
+      <c r="E54" s="3">
         <v>869500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>843300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>855400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>876900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>932300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>791300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>776400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>766700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>760200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>788100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>790000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>786800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>797300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>850600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>888200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>906400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>642800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>319300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>309700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>305100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>308000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>307700</v>
       </c>
     </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3766,8 +3895,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3793,8 +3923,9 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3802,70 +3933,73 @@
         <v>7000</v>
       </c>
       <c r="E57" s="3">
+        <v>7000</v>
+      </c>
+      <c r="F57" s="3">
         <v>7300</v>
-      </c>
-      <c r="F57" s="3">
-        <v>7900</v>
       </c>
       <c r="G57" s="3">
         <v>7900</v>
       </c>
       <c r="H57" s="3">
+        <v>7900</v>
+      </c>
+      <c r="I57" s="3">
         <v>8200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>7000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>5200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>6000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>8200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>7800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>7600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>5300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>4600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>4100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>5300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>4700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>4500</v>
       </c>
     </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3935,8 +4069,11 @@
       <c r="Y58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4006,8 +4143,11 @@
       <c r="Y59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -4077,8 +4217,11 @@
       <c r="Y60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4122,17 +4265,17 @@
         <v>0</v>
       </c>
       <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
         <v>105800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>130000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>129200</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
@@ -4148,8 +4291,11 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4219,8 +4365,11 @@
       <c r="Y62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4290,8 +4439,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4361,8 +4513,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4432,79 +4587,85 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>748500</v>
+      </c>
+      <c r="E66" s="3">
         <v>746200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>721700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>737000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>759000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>814000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>674200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>661200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>651300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>643900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>667100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>670300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>669200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>682000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>769800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>809000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>829100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>566900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>242100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>233200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>228300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>231700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>231300</v>
       </c>
     </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4530,8 +4691,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4601,8 +4763,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4672,8 +4837,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4743,8 +4911,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4814,79 +4985,85 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>73700</v>
+      </c>
+      <c r="E72" s="3">
         <v>72700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>71300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>69800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>68200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>66600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>65400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>63700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>61800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>60000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>58200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>56900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>55100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>52800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>50700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>49200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>47300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>46300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>47600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>47100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>47300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>47200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>47000</v>
       </c>
     </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4956,8 +5133,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5027,8 +5207,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5098,79 +5281,85 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>125100</v>
+      </c>
+      <c r="E76" s="3">
         <v>123300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>121500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>118500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>117900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>118300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>117100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>115200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>115400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>116400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>121000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>119700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>117600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>115300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>80800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>79200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>77200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>75900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>77200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>76500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>76800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>76300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>76400</v>
       </c>
     </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5240,146 +5429,152 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1500</v>
-      </c>
-      <c r="F81" s="3">
-        <v>1600</v>
       </c>
       <c r="G81" s="3">
         <v>1600</v>
       </c>
       <c r="H81" s="3">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="I81" s="3">
         <v>1700</v>
       </c>
       <c r="J81" s="3">
+        <v>1700</v>
+      </c>
+      <c r="K81" s="3">
         <v>1900</v>
-      </c>
-      <c r="K81" s="3">
-        <v>1800</v>
       </c>
       <c r="L81" s="3">
         <v>1800</v>
       </c>
       <c r="M81" s="3">
+        <v>1800</v>
+      </c>
+      <c r="N81" s="3">
         <v>1300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-1300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-200</v>
-      </c>
-      <c r="W81" s="3">
-        <v>100</v>
       </c>
       <c r="X81" s="3">
         <v>100</v>
@@ -5387,8 +5582,11 @@
       <c r="Y81" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5414,8 +5612,9 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5434,8 +5633,8 @@
       <c r="H83" s="3">
         <v>200</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>5</v>
+      <c r="I83" s="3">
+        <v>200</v>
       </c>
       <c r="J83" s="3" t="s">
         <v>5</v>
@@ -5449,18 +5648,18 @@
       <c r="M83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N83" s="3">
-        <v>0</v>
-      </c>
-      <c r="O83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P83" s="3">
+      <c r="N83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O83" s="3">
+        <v>0</v>
+      </c>
+      <c r="P83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q83" s="3">
         <v>200</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R83" s="3" t="s">
         <v>5</v>
       </c>
@@ -5470,14 +5669,14 @@
       <c r="T83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U83" s="3">
+      <c r="U83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V83" s="3">
         <v>200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>300</v>
-      </c>
-      <c r="W83" s="3">
-        <v>200</v>
       </c>
       <c r="X83" s="3">
         <v>200</v>
@@ -5485,8 +5684,11 @@
       <c r="Y83" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5556,8 +5758,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5627,8 +5832,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5698,8 +5906,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5769,8 +5980,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5840,79 +6054,85 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>600</v>
+      </c>
+      <c r="E89" s="3">
         <v>1200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>3800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>8700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>2400</v>
       </c>
-      <c r="S89" s="3">
-        <v>0</v>
-      </c>
       <c r="T89" s="3">
+        <v>0</v>
+      </c>
+      <c r="U89" s="3">
         <v>-2900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5938,8 +6158,9 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5947,10 +6168,10 @@
         <v>-100</v>
       </c>
       <c r="E91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F91" s="3">
         <v>-200</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-100</v>
       </c>
       <c r="G91" s="3">
         <v>-100</v>
@@ -5959,58 +6180,61 @@
         <v>-100</v>
       </c>
       <c r="I91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J91" s="3">
         <v>-500</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-300</v>
       </c>
       <c r="K91" s="3">
         <v>-300</v>
       </c>
       <c r="L91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M91" s="3">
         <v>-400</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-300</v>
       </c>
       <c r="N91" s="3">
         <v>-300</v>
       </c>
       <c r="O91" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-100</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
       <c r="T91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="U91" s="3">
         <v>-100</v>
       </c>
       <c r="V91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3">
         <v>-200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-100</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6080,8 +6304,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6151,79 +6378,85 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-13900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-14700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>1600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-29200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-26300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-26600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-23800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-17100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-17400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>11200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>23700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-27100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>33400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>5100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-115600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-33300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>13000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-7500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-7000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-4800</v>
       </c>
     </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6249,8 +6482,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6320,8 +6554,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6391,8 +6628,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6462,8 +6702,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6533,79 +6776,85 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E100" s="3">
         <v>24800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-14900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-22300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-56600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>137800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>12800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>9300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>7300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-28700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>3300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-13200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-58400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-36600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-22300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>261700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>36400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>9100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>6000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-3900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6675,75 +6924,81 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="E102" s="3">
         <v>11400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-11500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-21400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-54000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>110600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-14200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-14900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-14500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-41900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-19100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>15200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>14300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-76900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-14900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>146100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>10100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>18300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-11000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-6400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-3800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AFBI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AFBI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="92">
   <si>
     <t>AFBI</t>
   </si>
@@ -656,192 +656,199 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>11700</v>
+        <v>8000</v>
       </c>
       <c r="E8" s="3">
-        <v>10800</v>
+        <v>7900</v>
       </c>
       <c r="F8" s="3">
-        <v>10800</v>
+        <v>7300</v>
       </c>
       <c r="G8" s="3">
-        <v>10800</v>
+        <v>7400</v>
       </c>
       <c r="H8" s="3">
-        <v>10500</v>
+        <v>7500</v>
       </c>
       <c r="I8" s="3">
+        <v>7400</v>
+      </c>
+      <c r="J8" s="3">
+        <v>7400</v>
+      </c>
+      <c r="K8" s="3">
+        <v>9000</v>
+      </c>
+      <c r="L8" s="3">
+        <v>8200</v>
+      </c>
+      <c r="M8" s="3">
+        <v>7600</v>
+      </c>
+      <c r="N8" s="3">
+        <v>8300</v>
+      </c>
+      <c r="O8" s="3">
+        <v>7400</v>
+      </c>
+      <c r="P8" s="3">
+        <v>7600</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>8200</v>
+      </c>
+      <c r="R8" s="3">
         <v>9200</v>
       </c>
-      <c r="J8" s="3">
-        <v>9000</v>
-      </c>
-      <c r="K8" s="3">
-        <v>8200</v>
-      </c>
-      <c r="L8" s="3">
-        <v>7600</v>
-      </c>
-      <c r="M8" s="3">
-        <v>8300</v>
-      </c>
-      <c r="N8" s="3">
-        <v>7400</v>
-      </c>
-      <c r="O8" s="3">
-        <v>7600</v>
-      </c>
-      <c r="P8" s="3">
-        <v>8200</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>9200</v>
-      </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>8000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>8700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>7300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>6700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3800</v>
-      </c>
-      <c r="Y8" s="3">
-        <v>3600</v>
       </c>
       <c r="Z8" s="3">
         <v>3600</v>
       </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA8" s="3">
+        <v>3600</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -914,31 +921,34 @@
       <c r="Z9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>5</v>
+      <c r="D10" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>7900</v>
+      </c>
+      <c r="F10" s="3">
+        <v>7300</v>
+      </c>
+      <c r="G10" s="3">
+        <v>7400</v>
+      </c>
+      <c r="H10" s="3">
+        <v>7500</v>
+      </c>
+      <c r="I10" s="3">
+        <v>7400</v>
+      </c>
+      <c r="J10" s="3">
+        <v>7400</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>5</v>
@@ -988,8 +998,11 @@
       <c r="Z10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1016,8 +1029,9 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1090,8 +1104,11 @@
       <c r="Z12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1164,31 +1181,34 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1238,31 +1258,34 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1312,8 +1335,11 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1337,73 +1363,74 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>4300</v>
+        <v>5700</v>
       </c>
       <c r="E17" s="3">
-        <v>4000</v>
+        <v>6700</v>
       </c>
       <c r="F17" s="3">
-        <v>4000</v>
+        <v>5600</v>
       </c>
       <c r="G17" s="3">
-        <v>3900</v>
+        <v>5400</v>
       </c>
       <c r="H17" s="3">
-        <v>3800</v>
+        <v>5400</v>
       </c>
       <c r="I17" s="3">
-        <v>2300</v>
+        <v>5300</v>
       </c>
       <c r="J17" s="3">
+        <v>5200</v>
+      </c>
+      <c r="K17" s="3">
         <v>1700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>700</v>
-      </c>
-      <c r="M17" s="3">
-        <v>800</v>
       </c>
       <c r="N17" s="3">
         <v>800</v>
       </c>
       <c r="O17" s="3">
+        <v>800</v>
+      </c>
+      <c r="P17" s="3">
         <v>1000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1400</v>
-      </c>
-      <c r="T17" s="3">
-        <v>1500</v>
       </c>
       <c r="U17" s="3">
         <v>1500</v>
       </c>
       <c r="V17" s="3">
+        <v>1500</v>
+      </c>
+      <c r="W17" s="3">
         <v>700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>600</v>
-      </c>
-      <c r="X17" s="3">
-        <v>500</v>
       </c>
       <c r="Y17" s="3">
         <v>500</v>
@@ -1411,82 +1438,88 @@
       <c r="Z17" s="3">
         <v>500</v>
       </c>
-    </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA17" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E18" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F18" s="3">
+        <v>1800</v>
+      </c>
+      <c r="G18" s="3">
+        <v>1900</v>
+      </c>
+      <c r="H18" s="3">
+        <v>2100</v>
+      </c>
+      <c r="I18" s="3">
+        <v>2100</v>
+      </c>
+      <c r="J18" s="3">
+        <v>2200</v>
+      </c>
+      <c r="K18" s="3">
+        <v>7300</v>
+      </c>
+      <c r="L18" s="3">
         <v>7400</v>
       </c>
-      <c r="E18" s="3">
-        <v>6800</v>
-      </c>
-      <c r="F18" s="3">
-        <v>6800</v>
-      </c>
-      <c r="G18" s="3">
+      <c r="M18" s="3">
         <v>6900</v>
       </c>
-      <c r="H18" s="3">
-        <v>6700</v>
-      </c>
-      <c r="I18" s="3">
-        <v>6900</v>
-      </c>
-      <c r="J18" s="3">
-        <v>7300</v>
-      </c>
-      <c r="K18" s="3">
-        <v>7400</v>
-      </c>
-      <c r="L18" s="3">
-        <v>6900</v>
-      </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>7500</v>
-      </c>
-      <c r="N18" s="3">
-        <v>6600</v>
       </c>
       <c r="O18" s="3">
         <v>6600</v>
       </c>
       <c r="P18" s="3">
+        <v>6600</v>
+      </c>
+      <c r="Q18" s="3">
         <v>7100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>7800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>6900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>7300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>5800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>5200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>3100</v>
-      </c>
-      <c r="W18" s="3">
-        <v>3300</v>
       </c>
       <c r="X18" s="3">
         <v>3300</v>
       </c>
       <c r="Y18" s="3">
-        <v>3100</v>
+        <v>3300</v>
       </c>
       <c r="Z18" s="3">
         <v>3100</v>
       </c>
-    </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA18" s="3">
+        <v>3100</v>
+      </c>
+    </row>
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1513,106 +1546,110 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>-6000</v>
+      <c r="D20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K20" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="L20" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="M20" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="N20" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="O20" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="P20" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="R20" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="S20" s="3">
         <v>-5000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="T20" s="3">
         <v>-4800</v>
       </c>
-      <c r="G20" s="3">
-        <v>-4800</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-4600</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-4600</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-5100</v>
-      </c>
-      <c r="K20" s="3">
-        <v>-4900</v>
-      </c>
-      <c r="L20" s="3">
-        <v>-4600</v>
-      </c>
-      <c r="M20" s="3">
-        <v>-5200</v>
-      </c>
-      <c r="N20" s="3">
-        <v>-4800</v>
-      </c>
-      <c r="O20" s="3">
-        <v>-4200</v>
-      </c>
-      <c r="P20" s="3">
-        <v>-4100</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>-5100</v>
-      </c>
-      <c r="R20" s="3">
-        <v>-5000</v>
-      </c>
-      <c r="S20" s="3">
-        <v>-4800</v>
-      </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-4400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-7100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-2800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-3600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-3100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-3000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-2900</v>
       </c>
     </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E21" s="3">
         <v>1500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2100</v>
-      </c>
-      <c r="G21" s="3">
-        <v>2300</v>
       </c>
       <c r="H21" s="3">
         <v>2300</v>
       </c>
       <c r="I21" s="3">
+        <v>2300</v>
+      </c>
+      <c r="J21" s="3">
         <v>2400</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K21" s="3" t="s">
         <v>5</v>
       </c>
@@ -1631,12 +1668,12 @@
       <c r="P21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R21" s="3">
         <v>2900</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>5</v>
       </c>
@@ -1646,14 +1683,14 @@
       <c r="U21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V21" s="3">
+      <c r="V21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W21" s="3">
         <v>600</v>
       </c>
-      <c r="W21" s="3">
-        <v>0</v>
-      </c>
       <c r="X21" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="Y21" s="3">
         <v>300</v>
@@ -1661,31 +1698,34 @@
       <c r="Z21" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1735,96 +1775,102 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E23" s="3">
         <v>1300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1900</v>
-      </c>
-      <c r="G23" s="3">
-        <v>2100</v>
       </c>
       <c r="H23" s="3">
         <v>2100</v>
       </c>
       <c r="I23" s="3">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="J23" s="3">
         <v>2200</v>
       </c>
       <c r="K23" s="3">
+        <v>2200</v>
+      </c>
+      <c r="L23" s="3">
         <v>2400</v>
-      </c>
-      <c r="L23" s="3">
-        <v>2300</v>
       </c>
       <c r="M23" s="3">
         <v>2300</v>
       </c>
       <c r="N23" s="3">
+        <v>2300</v>
+      </c>
+      <c r="O23" s="3">
         <v>1800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>3000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-1800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-300</v>
-      </c>
-      <c r="X23" s="3">
-        <v>100</v>
       </c>
       <c r="Y23" s="3">
         <v>100</v>
       </c>
       <c r="Z23" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA23" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>500</v>
+      </c>
+      <c r="E24" s="3">
         <v>300</v>
-      </c>
-      <c r="E24" s="3">
-        <v>400</v>
       </c>
       <c r="F24" s="3">
         <v>400</v>
       </c>
       <c r="G24" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="H24" s="3">
         <v>500</v>
@@ -1836,55 +1882,58 @@
         <v>500</v>
       </c>
       <c r="K24" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="L24" s="3">
         <v>600</v>
       </c>
       <c r="M24" s="3">
+        <v>600</v>
+      </c>
+      <c r="N24" s="3">
         <v>500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-100</v>
       </c>
-      <c r="X24" s="3">
-        <v>0</v>
-      </c>
       <c r="Y24" s="3">
         <v>0</v>
       </c>
       <c r="Z24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1957,73 +2006,76 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E26" s="3">
         <v>1000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1500</v>
-      </c>
-      <c r="G26" s="3">
-        <v>1600</v>
       </c>
       <c r="H26" s="3">
         <v>1600</v>
       </c>
       <c r="I26" s="3">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="J26" s="3">
         <v>1700</v>
       </c>
       <c r="K26" s="3">
+        <v>1700</v>
+      </c>
+      <c r="L26" s="3">
         <v>1900</v>
-      </c>
-      <c r="L26" s="3">
-        <v>1800</v>
       </c>
       <c r="M26" s="3">
         <v>1800</v>
       </c>
       <c r="N26" s="3">
+        <v>1800</v>
+      </c>
+      <c r="O26" s="3">
         <v>1300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-1300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-200</v>
-      </c>
-      <c r="X26" s="3">
-        <v>100</v>
       </c>
       <c r="Y26" s="3">
         <v>100</v>
@@ -2031,73 +2083,76 @@
       <c r="Z26" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA26" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E27" s="3">
         <v>1000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1500</v>
-      </c>
-      <c r="G27" s="3">
-        <v>1600</v>
       </c>
       <c r="H27" s="3">
         <v>1600</v>
       </c>
       <c r="I27" s="3">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="J27" s="3">
         <v>1700</v>
       </c>
       <c r="K27" s="3">
+        <v>1700</v>
+      </c>
+      <c r="L27" s="3">
         <v>1900</v>
-      </c>
-      <c r="L27" s="3">
-        <v>1800</v>
       </c>
       <c r="M27" s="3">
         <v>1800</v>
       </c>
       <c r="N27" s="3">
+        <v>1800</v>
+      </c>
+      <c r="O27" s="3">
         <v>1300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-1300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-200</v>
-      </c>
-      <c r="X27" s="3">
-        <v>100</v>
       </c>
       <c r="Y27" s="3">
         <v>100</v>
@@ -2105,8 +2160,11 @@
       <c r="Z27" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA27" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2179,8 +2237,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2235,8 +2296,8 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>5</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>5</v>
@@ -2253,8 +2314,11 @@
       <c r="Z29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2327,8 +2391,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2401,147 +2468,153 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>6000</v>
+      <c r="D32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E32" s="3">
+        <v>100</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K32" s="3">
+        <v>5100</v>
+      </c>
+      <c r="L32" s="3">
+        <v>4900</v>
+      </c>
+      <c r="M32" s="3">
+        <v>4600</v>
+      </c>
+      <c r="N32" s="3">
+        <v>5200</v>
+      </c>
+      <c r="O32" s="3">
+        <v>4800</v>
+      </c>
+      <c r="P32" s="3">
+        <v>4200</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>4100</v>
+      </c>
+      <c r="R32" s="3">
+        <v>5100</v>
+      </c>
+      <c r="S32" s="3">
         <v>5000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="T32" s="3">
         <v>4800</v>
       </c>
-      <c r="G32" s="3">
-        <v>4800</v>
-      </c>
-      <c r="H32" s="3">
-        <v>4600</v>
-      </c>
-      <c r="I32" s="3">
-        <v>4600</v>
-      </c>
-      <c r="J32" s="3">
-        <v>5100</v>
-      </c>
-      <c r="K32" s="3">
-        <v>4900</v>
-      </c>
-      <c r="L32" s="3">
-        <v>4600</v>
-      </c>
-      <c r="M32" s="3">
-        <v>5200</v>
-      </c>
-      <c r="N32" s="3">
-        <v>4800</v>
-      </c>
-      <c r="O32" s="3">
-        <v>4200</v>
-      </c>
-      <c r="P32" s="3">
-        <v>4100</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>5100</v>
-      </c>
-      <c r="R32" s="3">
-        <v>5000</v>
-      </c>
-      <c r="S32" s="3">
-        <v>4800</v>
-      </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>4400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>7100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>2800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>3600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>3100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>3000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E33" s="3">
         <v>1000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1500</v>
-      </c>
-      <c r="G33" s="3">
-        <v>1600</v>
       </c>
       <c r="H33" s="3">
         <v>1600</v>
       </c>
       <c r="I33" s="3">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="J33" s="3">
         <v>1700</v>
       </c>
       <c r="K33" s="3">
+        <v>1700</v>
+      </c>
+      <c r="L33" s="3">
         <v>1900</v>
-      </c>
-      <c r="L33" s="3">
-        <v>1800</v>
       </c>
       <c r="M33" s="3">
         <v>1800</v>
       </c>
       <c r="N33" s="3">
+        <v>1800</v>
+      </c>
+      <c r="O33" s="3">
         <v>1300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-1300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-200</v>
-      </c>
-      <c r="X33" s="3">
-        <v>100</v>
       </c>
       <c r="Y33" s="3">
         <v>100</v>
@@ -2549,8 +2622,11 @@
       <c r="Z33" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA33" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2623,73 +2699,76 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E35" s="3">
         <v>1000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1500</v>
-      </c>
-      <c r="G35" s="3">
-        <v>1600</v>
       </c>
       <c r="H35" s="3">
         <v>1600</v>
       </c>
       <c r="I35" s="3">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="J35" s="3">
         <v>1700</v>
       </c>
       <c r="K35" s="3">
+        <v>1700</v>
+      </c>
+      <c r="L35" s="3">
         <v>1900</v>
-      </c>
-      <c r="L35" s="3">
-        <v>1800</v>
       </c>
       <c r="M35" s="3">
         <v>1800</v>
       </c>
       <c r="N35" s="3">
+        <v>1800</v>
+      </c>
+      <c r="O35" s="3">
         <v>1300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-1300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-200</v>
-      </c>
-      <c r="X35" s="3">
-        <v>100</v>
       </c>
       <c r="Y35" s="3">
         <v>100</v>
@@ -2697,87 +2776,93 @@
       <c r="Z35" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA35" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2804,8 +2889,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2832,179 +2918,186 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>52300</v>
+      </c>
+      <c r="E41" s="3">
+        <v>50400</v>
+      </c>
+      <c r="F41" s="3">
+        <v>61400</v>
+      </c>
+      <c r="G41" s="3">
+        <v>50000</v>
+      </c>
+      <c r="H41" s="3">
+        <v>61500</v>
+      </c>
+      <c r="I41" s="3">
+        <v>82900</v>
+      </c>
+      <c r="J41" s="3">
+        <v>136900</v>
+      </c>
+      <c r="K41" s="3">
+        <v>2900</v>
+      </c>
+      <c r="L41" s="3">
+        <v>6900</v>
+      </c>
+      <c r="M41" s="3">
+        <v>8100</v>
+      </c>
+      <c r="N41" s="3">
+        <v>14300</v>
+      </c>
+      <c r="O41" s="3">
+        <v>16200</v>
+      </c>
+      <c r="P41" s="3">
+        <v>17300</v>
+      </c>
+      <c r="Q41" s="3">
+        <v>15300</v>
+      </c>
+      <c r="R41" s="3">
+        <v>10000</v>
+      </c>
+      <c r="S41" s="3">
+        <v>5600</v>
+      </c>
+      <c r="T41" s="3">
         <v>6200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="U41" s="3">
+        <v>14300</v>
+      </c>
+      <c r="V41" s="3">
         <v>6400</v>
       </c>
-      <c r="F41" s="3">
-        <v>6000</v>
-      </c>
-      <c r="G41" s="3">
-        <v>5400</v>
-      </c>
-      <c r="H41" s="3">
-        <v>7100</v>
-      </c>
-      <c r="I41" s="3">
-        <v>5700</v>
-      </c>
-      <c r="J41" s="3">
-        <v>2900</v>
-      </c>
-      <c r="K41" s="3">
-        <v>6900</v>
-      </c>
-      <c r="L41" s="3">
-        <v>8100</v>
-      </c>
-      <c r="M41" s="3">
-        <v>14300</v>
-      </c>
-      <c r="N41" s="3">
-        <v>16200</v>
-      </c>
-      <c r="O41" s="3">
-        <v>17300</v>
-      </c>
-      <c r="P41" s="3">
-        <v>15300</v>
-      </c>
-      <c r="Q41" s="3">
-        <v>10000</v>
-      </c>
-      <c r="R41" s="3">
-        <v>5600</v>
-      </c>
-      <c r="S41" s="3">
-        <v>6200</v>
-      </c>
-      <c r="T41" s="3">
-        <v>14300</v>
-      </c>
-      <c r="U41" s="3">
-        <v>6400</v>
-      </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>4000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>3300</v>
-      </c>
-      <c r="X41" s="3">
-        <v>4600</v>
       </c>
       <c r="Y41" s="3">
         <v>4600</v>
       </c>
       <c r="Z41" s="3">
+        <v>4600</v>
+      </c>
+      <c r="AA41" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>66200</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>77700</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>66300</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>77700</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>94000</v>
+        <v>0</v>
       </c>
       <c r="I42" s="3">
-        <v>151500</v>
+        <v>0</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>37000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>43900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>57700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>66100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>107300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>122700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>109000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>97600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>176900</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>178200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>185600</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>47200</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>44400</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>35000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>15400</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>26300</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>33800</v>
       </c>
     </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>0</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+      <c r="D43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -3054,31 +3147,34 @@
       <c r="Z43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F44" s="3">
-        <v>0</v>
+        <v>2900</v>
       </c>
       <c r="G44" s="3">
-        <v>0</v>
+        <v>2900</v>
       </c>
       <c r="H44" s="3">
-        <v>0</v>
+        <v>2900</v>
       </c>
       <c r="I44" s="3">
-        <v>0</v>
+        <v>2900</v>
       </c>
       <c r="J44" s="3">
-        <v>0</v>
+        <v>2900</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3128,31 +3224,34 @@
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>2400</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <v>2400</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
-      </c>
-      <c r="G45" s="3">
-        <v>0</v>
+        <v>2200</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="I45" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -3202,31 +3301,34 @@
       <c r="Z45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>54700</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>52800</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>66400</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>52900</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>66300</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>87500</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>141400</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -3276,31 +3378,34 @@
       <c r="Z46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
+        <v>86800</v>
       </c>
       <c r="E47" s="3">
-        <v>0</v>
+        <v>87000</v>
       </c>
       <c r="F47" s="3">
-        <v>0</v>
+        <v>87900</v>
       </c>
       <c r="G47" s="3">
-        <v>0</v>
+        <v>88200</v>
       </c>
       <c r="H47" s="3">
-        <v>0</v>
+        <v>87100</v>
       </c>
       <c r="I47" s="3">
-        <v>0</v>
+        <v>85600</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>88300</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -3350,111 +3455,117 @@
       <c r="Z47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E48" s="3">
         <v>3600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3700</v>
       </c>
-      <c r="F48" s="3">
-        <v>3800</v>
-      </c>
       <c r="G48" s="3">
+        <v>5500</v>
+      </c>
+      <c r="H48" s="3">
         <v>3900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4100</v>
-      </c>
-      <c r="L48" s="3">
-        <v>4000</v>
       </c>
       <c r="M48" s="3">
         <v>4000</v>
       </c>
       <c r="N48" s="3">
+        <v>4000</v>
+      </c>
+      <c r="O48" s="3">
         <v>3800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>7400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>7500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>7600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>8600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>8800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>8900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>9500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>8500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>8600</v>
-      </c>
-      <c r="X48" s="3">
-        <v>8800</v>
       </c>
       <c r="Y48" s="3">
         <v>8800</v>
       </c>
       <c r="Z48" s="3">
+        <v>8800</v>
+      </c>
+      <c r="AA48" s="3">
         <v>8900</v>
       </c>
     </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>18300</v>
+        <v>18200</v>
       </c>
       <c r="E49" s="3">
         <v>18300</v>
       </c>
       <c r="F49" s="3">
-        <v>18400</v>
+        <v>18300</v>
       </c>
       <c r="G49" s="3">
         <v>18400</v>
       </c>
       <c r="H49" s="3">
-        <v>18500</v>
+        <v>18400</v>
       </c>
       <c r="I49" s="3">
         <v>18500</v>
       </c>
       <c r="J49" s="3">
-        <v>18600</v>
+        <v>18500</v>
       </c>
       <c r="K49" s="3">
         <v>18600</v>
       </c>
       <c r="L49" s="3">
-        <v>18700</v>
+        <v>18600</v>
       </c>
       <c r="M49" s="3">
         <v>18700</v>
@@ -3463,29 +3574,29 @@
         <v>18700</v>
       </c>
       <c r="O49" s="3">
-        <v>18800</v>
+        <v>18700</v>
       </c>
       <c r="P49" s="3">
         <v>18800</v>
       </c>
       <c r="Q49" s="3">
-        <v>18900</v>
+        <v>18800</v>
       </c>
       <c r="R49" s="3">
         <v>18900</v>
       </c>
       <c r="S49" s="3">
-        <v>19000</v>
+        <v>18900</v>
       </c>
       <c r="T49" s="3">
         <v>19000</v>
       </c>
       <c r="U49" s="3">
+        <v>19000</v>
+      </c>
+      <c r="V49" s="3">
         <v>19100</v>
       </c>
-      <c r="V49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W49" s="3" t="s">
         <v>5</v>
       </c>
@@ -3498,8 +3609,11 @@
       <c r="Z49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3572,8 +3686,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3646,31 +3763,34 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>0</v>
+        <v>26200</v>
       </c>
       <c r="E52" s="3">
-        <v>0</v>
+        <v>27800</v>
       </c>
       <c r="F52" s="3">
-        <v>0</v>
+        <v>27200</v>
       </c>
       <c r="G52" s="3">
-        <v>0</v>
+        <v>27300</v>
       </c>
       <c r="H52" s="3">
-        <v>0</v>
+        <v>28000</v>
       </c>
       <c r="I52" s="3">
-        <v>0</v>
+        <v>27400</v>
       </c>
       <c r="J52" s="3">
-        <v>0</v>
+        <v>27800</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -3720,8 +3840,11 @@
       <c r="Z52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3794,82 +3917,88 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>878600</v>
+      </c>
+      <c r="E54" s="3">
         <v>873600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>869500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>843300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>855400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>876900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>932300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>791300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>776400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>766700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>760200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>788100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>790000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>786800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>797300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>850600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>888200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>906400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>642800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>319300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>309700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>305100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>308000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>307700</v>
       </c>
     </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3896,8 +4025,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3924,87 +4054,91 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>683800</v>
+      </c>
+      <c r="E57" s="3">
+        <v>689700</v>
+      </c>
+      <c r="F57" s="3">
+        <v>687400</v>
+      </c>
+      <c r="G57" s="3">
+        <v>674400</v>
+      </c>
+      <c r="H57" s="3">
+        <v>709000</v>
+      </c>
+      <c r="I57" s="3">
+        <v>731000</v>
+      </c>
+      <c r="J57" s="3">
+        <v>750800</v>
+      </c>
+      <c r="K57" s="3">
         <v>7000</v>
       </c>
-      <c r="E57" s="3">
-        <v>7000</v>
-      </c>
-      <c r="F57" s="3">
-        <v>7300</v>
-      </c>
-      <c r="G57" s="3">
-        <v>7900</v>
-      </c>
-      <c r="H57" s="3">
-        <v>7900</v>
-      </c>
-      <c r="I57" s="3">
+      <c r="L57" s="3">
+        <v>5200</v>
+      </c>
+      <c r="M57" s="3">
+        <v>5100</v>
+      </c>
+      <c r="N57" s="3">
+        <v>5800</v>
+      </c>
+      <c r="O57" s="3">
+        <v>3300</v>
+      </c>
+      <c r="P57" s="3">
+        <v>6000</v>
+      </c>
+      <c r="Q57" s="3">
         <v>8200</v>
       </c>
-      <c r="J57" s="3">
-        <v>7000</v>
-      </c>
-      <c r="K57" s="3">
-        <v>5200</v>
-      </c>
-      <c r="L57" s="3">
-        <v>5100</v>
-      </c>
-      <c r="M57" s="3">
-        <v>5800</v>
-      </c>
-      <c r="N57" s="3">
-        <v>3300</v>
-      </c>
-      <c r="O57" s="3">
-        <v>6000</v>
-      </c>
-      <c r="P57" s="3">
-        <v>8200</v>
-      </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>7800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>4700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>7600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>5300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>4600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>4100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>5300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>4700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>4500</v>
       </c>
     </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>4800</v>
       </c>
       <c r="E58" s="3">
         <v>0</v>
@@ -4013,7 +4147,7 @@
         <v>0</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="H58" s="3">
         <v>0</v>
@@ -4022,7 +4156,7 @@
         <v>0</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -4072,31 +4206,34 @@
       <c r="Z58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>0</v>
-      </c>
-      <c r="E59" s="3">
-        <v>0</v>
-      </c>
-      <c r="F59" s="3">
-        <v>0</v>
-      </c>
-      <c r="G59" s="3">
-        <v>0</v>
-      </c>
-      <c r="H59" s="3">
-        <v>0</v>
-      </c>
-      <c r="I59" s="3">
-        <v>0</v>
-      </c>
-      <c r="J59" s="3">
-        <v>0</v>
+      <c r="D59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K59" s="3">
         <v>0</v>
@@ -4146,31 +4283,34 @@
       <c r="Z59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>695400</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>696700</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>694400</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>678100</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>717000</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>739000</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>774000</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -4220,31 +4360,34 @@
       <c r="Z60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>54000</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>51800</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>51800</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>41500</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -4268,17 +4411,17 @@
         <v>0</v>
       </c>
       <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3">
         <v>105800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>130000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>129200</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
@@ -4294,31 +4437,34 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
-      </c>
-      <c r="E62" s="3">
-        <v>0</v>
-      </c>
-      <c r="F62" s="3">
-        <v>0</v>
+        <v>700</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G62" s="3">
-        <v>0</v>
-      </c>
-      <c r="H62" s="3">
-        <v>0</v>
-      </c>
-      <c r="I62" s="3">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3">
-        <v>0</v>
+        <v>1600</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -4368,8 +4514,11 @@
       <c r="Z62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4442,8 +4591,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4516,8 +4668,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4590,82 +4745,88 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>750200</v>
+      </c>
+      <c r="E66" s="3">
         <v>748500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>746200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>721700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>737000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>759000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>814000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>674200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>661200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>651300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>643900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>667100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>670300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>669200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>682000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>769800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>809000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>829100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>566900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>242100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>233200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>228300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>231700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>231300</v>
       </c>
     </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4692,8 +4853,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4766,8 +4928,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4840,8 +5005,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4914,8 +5082,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4988,82 +5159,88 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>75400</v>
+      </c>
+      <c r="E72" s="3">
         <v>73700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>72700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>71300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>69800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>68200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>66600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>65400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>63700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>61800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>60000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>58200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>56900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>55100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>52800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>50700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>49200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>47300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>46300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>47600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>47100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>47300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>47200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>47000</v>
       </c>
     </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5136,8 +5313,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5210,8 +5390,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5284,82 +5467,88 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>128400</v>
+      </c>
+      <c r="E76" s="3">
         <v>125100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>123300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>121500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>118500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>117900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>118300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>117100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>115200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>115400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>116400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>121000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>119700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>117600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>115300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>80800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>79200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>77200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>75900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>77200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>76500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>76800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>76300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>76400</v>
       </c>
     </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5432,152 +5621,158 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E81" s="3">
         <v>1000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1500</v>
-      </c>
-      <c r="G81" s="3">
-        <v>1600</v>
       </c>
       <c r="H81" s="3">
         <v>1600</v>
       </c>
       <c r="I81" s="3">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="J81" s="3">
         <v>1700</v>
       </c>
       <c r="K81" s="3">
+        <v>1700</v>
+      </c>
+      <c r="L81" s="3">
         <v>1900</v>
-      </c>
-      <c r="L81" s="3">
-        <v>1800</v>
       </c>
       <c r="M81" s="3">
         <v>1800</v>
       </c>
       <c r="N81" s="3">
+        <v>1800</v>
+      </c>
+      <c r="O81" s="3">
         <v>1300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-1300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-200</v>
-      </c>
-      <c r="X81" s="3">
-        <v>100</v>
       </c>
       <c r="Y81" s="3">
         <v>100</v>
@@ -5585,8 +5780,11 @@
       <c r="Z81" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA81" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5613,31 +5811,32 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E83" s="3">
         <v>200</v>
       </c>
       <c r="F83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G83" s="3">
-        <v>200</v>
+        <v>700</v>
       </c>
       <c r="H83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="I83" s="3">
         <v>200</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>5</v>
+      <c r="J83" s="3">
+        <v>-900</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>5</v>
@@ -5651,18 +5850,18 @@
       <c r="N83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O83" s="3">
-        <v>0</v>
-      </c>
-      <c r="P83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q83" s="3">
+      <c r="O83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R83" s="3">
         <v>200</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S83" s="3" t="s">
         <v>5</v>
       </c>
@@ -5672,14 +5871,14 @@
       <c r="U83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V83" s="3">
+      <c r="V83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W83" s="3">
         <v>200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>300</v>
-      </c>
-      <c r="X83" s="3">
-        <v>200</v>
       </c>
       <c r="Y83" s="3">
         <v>200</v>
@@ -5687,8 +5886,11 @@
       <c r="Z83" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5761,8 +5963,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5835,8 +6040,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5909,8 +6117,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5983,8 +6194,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6057,82 +6271,88 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E89" s="3">
         <v>600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>3800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>8700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>2400</v>
       </c>
-      <c r="T89" s="3">
-        <v>0</v>
-      </c>
       <c r="U89" s="3">
+        <v>0</v>
+      </c>
+      <c r="V89" s="3">
         <v>-2900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6159,8 +6379,9 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6171,10 +6392,10 @@
         <v>-100</v>
       </c>
       <c r="F91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G91" s="3">
         <v>-200</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-100</v>
       </c>
       <c r="H91" s="3">
         <v>-100</v>
@@ -6183,58 +6404,61 @@
         <v>-100</v>
       </c>
       <c r="J91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K91" s="3">
         <v>-500</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-300</v>
       </c>
       <c r="L91" s="3">
         <v>-300</v>
       </c>
       <c r="M91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="N91" s="3">
         <v>-400</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-300</v>
       </c>
       <c r="O91" s="3">
         <v>-300</v>
       </c>
       <c r="P91" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-100</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
       <c r="U91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="V91" s="3">
         <v>-100</v>
       </c>
       <c r="W91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-100</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6307,8 +6531,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6381,82 +6608,88 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-13900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-14700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>1600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-29200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-26300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-26600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-23800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-17100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-17400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>11200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>23700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-27100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>33400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>5100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-115600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-33300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>13000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-7500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-7000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-4800</v>
       </c>
     </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6483,31 +6716,32 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -6557,8 +6791,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6631,8 +6868,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6705,8 +6945,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6779,105 +7022,111 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E100" s="3">
         <v>2300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>24800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-14900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-22300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-56600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>137800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>12800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>9300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>7300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-28700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>3300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-13200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-58400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-36600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-22300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>261700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>36400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>9100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>6000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-3900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -6927,78 +7176,84 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-11000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>11400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-11500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-21400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-54000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>110600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-14200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-14900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-14500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-41900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-19100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>15200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>14300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-76900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-14900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>146100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>10100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>18300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-11000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-6400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-3800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AFBI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AFBI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="92">
   <si>
     <t>AFBI</t>
   </si>
@@ -656,199 +656,205 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E8" s="3">
         <v>8000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>7900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>7300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>7400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>7500</v>
-      </c>
-      <c r="I8" s="3">
-        <v>7400</v>
       </c>
       <c r="J8" s="3">
         <v>7400</v>
       </c>
       <c r="K8" s="3">
+        <v>7400</v>
+      </c>
+      <c r="L8" s="3">
         <v>9000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>8200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>7600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>8300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>7400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>7600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>8200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>9200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>8000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>8700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>7300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>6700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3800</v>
-      </c>
-      <c r="Z8" s="3">
-        <v>3600</v>
       </c>
       <c r="AA8" s="3">
         <v>3600</v>
       </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3">
+        <v>3600</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -924,34 +930,37 @@
       <c r="AA9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E10" s="3">
         <v>8000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>7900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>7300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>7400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>7500</v>
-      </c>
-      <c r="I10" s="3">
-        <v>7400</v>
       </c>
       <c r="J10" s="3">
         <v>7400</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>5</v>
+      <c r="K10" s="3">
+        <v>7400</v>
       </c>
       <c r="L10" s="3" t="s">
         <v>5</v>
@@ -1001,8 +1010,11 @@
       <c r="AA10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1030,8 +1042,9 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1107,8 +1120,11 @@
       <c r="AA12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1184,8 +1200,11 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1210,8 +1229,8 @@
       <c r="J14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1261,8 +1280,11 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1288,7 +1310,7 @@
         <v>200</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -1338,8 +1360,11 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1364,76 +1389,77 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E17" s="3">
         <v>5700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>6700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>5600</v>
-      </c>
-      <c r="G17" s="3">
-        <v>5400</v>
       </c>
       <c r="H17" s="3">
         <v>5400</v>
       </c>
       <c r="I17" s="3">
+        <v>5400</v>
+      </c>
+      <c r="J17" s="3">
         <v>5300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>700</v>
-      </c>
-      <c r="N17" s="3">
-        <v>800</v>
       </c>
       <c r="O17" s="3">
         <v>800</v>
       </c>
       <c r="P17" s="3">
+        <v>800</v>
+      </c>
+      <c r="Q17" s="3">
         <v>1000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1400</v>
-      </c>
-      <c r="U17" s="3">
-        <v>1500</v>
       </c>
       <c r="V17" s="3">
         <v>1500</v>
       </c>
       <c r="W17" s="3">
+        <v>1500</v>
+      </c>
+      <c r="X17" s="3">
         <v>700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>600</v>
-      </c>
-      <c r="Y17" s="3">
-        <v>500</v>
       </c>
       <c r="Z17" s="3">
         <v>500</v>
@@ -1441,85 +1467,91 @@
       <c r="AA17" s="3">
         <v>500</v>
       </c>
-    </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB17" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E18" s="3">
         <v>2300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1900</v>
-      </c>
-      <c r="H18" s="3">
-        <v>2100</v>
       </c>
       <c r="I18" s="3">
         <v>2100</v>
       </c>
       <c r="J18" s="3">
+        <v>2100</v>
+      </c>
+      <c r="K18" s="3">
         <v>2200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>7300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>7400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>6900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>7500</v>
-      </c>
-      <c r="O18" s="3">
-        <v>6600</v>
       </c>
       <c r="P18" s="3">
         <v>6600</v>
       </c>
       <c r="Q18" s="3">
+        <v>6600</v>
+      </c>
+      <c r="R18" s="3">
         <v>7100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>7800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>6900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>7300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>5800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>5200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>3100</v>
-      </c>
-      <c r="X18" s="3">
-        <v>3300</v>
       </c>
       <c r="Y18" s="3">
         <v>3300</v>
       </c>
       <c r="Z18" s="3">
-        <v>3100</v>
+        <v>3300</v>
       </c>
       <c r="AA18" s="3">
         <v>3100</v>
       </c>
-    </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB18" s="3">
+        <v>3100</v>
+      </c>
+    </row>
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1547,20 +1579,21 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E20" s="3">
+      <c r="E20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20" s="3">
         <v>-100</v>
       </c>
-      <c r="F20" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G20" s="3" t="s">
         <v>5</v>
       </c>
@@ -1573,86 +1606,89 @@
       <c r="J20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L20" s="3">
         <v>-5100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-4900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-4600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-5200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-4800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-4200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-4100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-5100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-5000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-4800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-4400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-7100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-2800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-3600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-3100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-3000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-2900</v>
       </c>
     </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E21" s="3">
         <v>2400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2100</v>
-      </c>
-      <c r="H21" s="3">
-        <v>2300</v>
       </c>
       <c r="I21" s="3">
         <v>2300</v>
       </c>
       <c r="J21" s="3">
+        <v>2300</v>
+      </c>
+      <c r="K21" s="3">
         <v>2400</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>5</v>
       </c>
@@ -1671,12 +1707,12 @@
       <c r="Q21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R21" s="3">
+      <c r="R21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S21" s="3">
         <v>2900</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>5</v>
       </c>
@@ -1686,14 +1722,14 @@
       <c r="V21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W21" s="3">
+      <c r="W21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X21" s="3">
         <v>600</v>
       </c>
-      <c r="X21" s="3">
-        <v>0</v>
-      </c>
       <c r="Y21" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="Z21" s="3">
         <v>300</v>
@@ -1701,8 +1737,11 @@
       <c r="AA21" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1727,8 +1766,8 @@
       <c r="J22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1778,102 +1817,108 @@
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E23" s="3">
         <v>2300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1900</v>
-      </c>
-      <c r="H23" s="3">
-        <v>2100</v>
       </c>
       <c r="I23" s="3">
         <v>2100</v>
       </c>
       <c r="J23" s="3">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="K23" s="3">
         <v>2200</v>
       </c>
       <c r="L23" s="3">
+        <v>2200</v>
+      </c>
+      <c r="M23" s="3">
         <v>2400</v>
-      </c>
-      <c r="M23" s="3">
-        <v>2300</v>
       </c>
       <c r="N23" s="3">
         <v>2300</v>
       </c>
       <c r="O23" s="3">
+        <v>2300</v>
+      </c>
+      <c r="P23" s="3">
         <v>1800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>3000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-1800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-300</v>
-      </c>
-      <c r="Y23" s="3">
-        <v>100</v>
       </c>
       <c r="Z23" s="3">
         <v>100</v>
       </c>
       <c r="AA23" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB23" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>300</v>
+      </c>
+      <c r="E24" s="3">
         <v>500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>300</v>
-      </c>
-      <c r="F24" s="3">
-        <v>400</v>
       </c>
       <c r="G24" s="3">
         <v>400</v>
       </c>
       <c r="H24" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="I24" s="3">
         <v>500</v>
@@ -1885,55 +1930,58 @@
         <v>500</v>
       </c>
       <c r="L24" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="M24" s="3">
         <v>600</v>
       </c>
       <c r="N24" s="3">
+        <v>600</v>
+      </c>
+      <c r="O24" s="3">
         <v>500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-100</v>
       </c>
-      <c r="Y24" s="3">
-        <v>0</v>
-      </c>
       <c r="Z24" s="3">
         <v>0</v>
       </c>
       <c r="AA24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2009,76 +2057,79 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E26" s="3">
         <v>1700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1500</v>
-      </c>
-      <c r="H26" s="3">
-        <v>1600</v>
       </c>
       <c r="I26" s="3">
         <v>1600</v>
       </c>
       <c r="J26" s="3">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="K26" s="3">
         <v>1700</v>
       </c>
       <c r="L26" s="3">
+        <v>1700</v>
+      </c>
+      <c r="M26" s="3">
         <v>1900</v>
-      </c>
-      <c r="M26" s="3">
-        <v>1800</v>
       </c>
       <c r="N26" s="3">
         <v>1800</v>
       </c>
       <c r="O26" s="3">
+        <v>1800</v>
+      </c>
+      <c r="P26" s="3">
         <v>1300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-1300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-200</v>
-      </c>
-      <c r="Y26" s="3">
-        <v>100</v>
       </c>
       <c r="Z26" s="3">
         <v>100</v>
@@ -2086,76 +2137,79 @@
       <c r="AA26" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB26" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E27" s="3">
         <v>1700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1500</v>
-      </c>
-      <c r="H27" s="3">
-        <v>1600</v>
       </c>
       <c r="I27" s="3">
         <v>1600</v>
       </c>
       <c r="J27" s="3">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="K27" s="3">
         <v>1700</v>
       </c>
       <c r="L27" s="3">
+        <v>1700</v>
+      </c>
+      <c r="M27" s="3">
         <v>1900</v>
-      </c>
-      <c r="M27" s="3">
-        <v>1800</v>
       </c>
       <c r="N27" s="3">
         <v>1800</v>
       </c>
       <c r="O27" s="3">
+        <v>1800</v>
+      </c>
+      <c r="P27" s="3">
         <v>1300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-1300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-200</v>
-      </c>
-      <c r="Y27" s="3">
-        <v>100</v>
       </c>
       <c r="Z27" s="3">
         <v>100</v>
@@ -2163,8 +2217,11 @@
       <c r="AA27" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB27" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2240,8 +2297,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2299,8 +2359,8 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>5</v>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>5</v>
@@ -2317,8 +2377,11 @@
       <c r="AA29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2394,8 +2457,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2471,20 +2537,23 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E32" s="3">
+      <c r="E32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F32" s="3">
         <v>100</v>
       </c>
-      <c r="F32" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G32" s="3" t="s">
         <v>5</v>
       </c>
@@ -2497,127 +2566,130 @@
       <c r="J32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L32" s="3">
         <v>5100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>4900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>4600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>5200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>4800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>4200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>4100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>5100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>5000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>4800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>4400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>7100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>2800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>3600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>3100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>3000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E33" s="3">
         <v>1700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1500</v>
-      </c>
-      <c r="H33" s="3">
-        <v>1600</v>
       </c>
       <c r="I33" s="3">
         <v>1600</v>
       </c>
       <c r="J33" s="3">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="K33" s="3">
         <v>1700</v>
       </c>
       <c r="L33" s="3">
+        <v>1700</v>
+      </c>
+      <c r="M33" s="3">
         <v>1900</v>
-      </c>
-      <c r="M33" s="3">
-        <v>1800</v>
       </c>
       <c r="N33" s="3">
         <v>1800</v>
       </c>
       <c r="O33" s="3">
+        <v>1800</v>
+      </c>
+      <c r="P33" s="3">
         <v>1300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-1300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-200</v>
-      </c>
-      <c r="Y33" s="3">
-        <v>100</v>
       </c>
       <c r="Z33" s="3">
         <v>100</v>
@@ -2625,8 +2697,11 @@
       <c r="AA33" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB33" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2702,76 +2777,79 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E35" s="3">
         <v>1700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1500</v>
-      </c>
-      <c r="H35" s="3">
-        <v>1600</v>
       </c>
       <c r="I35" s="3">
         <v>1600</v>
       </c>
       <c r="J35" s="3">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="K35" s="3">
         <v>1700</v>
       </c>
       <c r="L35" s="3">
+        <v>1700</v>
+      </c>
+      <c r="M35" s="3">
         <v>1900</v>
-      </c>
-      <c r="M35" s="3">
-        <v>1800</v>
       </c>
       <c r="N35" s="3">
         <v>1800</v>
       </c>
       <c r="O35" s="3">
+        <v>1800</v>
+      </c>
+      <c r="P35" s="3">
         <v>1300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-1300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-200</v>
-      </c>
-      <c r="Y35" s="3">
-        <v>100</v>
       </c>
       <c r="Z35" s="3">
         <v>100</v>
@@ -2779,90 +2857,96 @@
       <c r="AA35" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB35" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2890,8 +2974,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2919,85 +3004,89 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>41400</v>
+      </c>
+      <c r="E41" s="3">
         <v>52300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>50400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>61400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>50000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>61500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>82900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>136900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>8100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>14300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>16200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>17300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>15300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>10000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>5600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>6200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>14300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>6400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>4000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>3300</v>
-      </c>
-      <c r="Y41" s="3">
-        <v>4600</v>
       </c>
       <c r="Z41" s="3">
         <v>4600</v>
       </c>
       <c r="AA41" s="3">
+        <v>4600</v>
+      </c>
+      <c r="AB41" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3023,58 +3112,61 @@
         <v>0</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>37000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>43900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>57700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>66100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>107300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>122700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>109000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>97600</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>176900</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>178200</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>185600</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>47200</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>44400</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>35000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>15400</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>26300</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>33800</v>
       </c>
     </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3099,8 +3191,8 @@
       <c r="J43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -3150,8 +3242,11 @@
       <c r="AA43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3161,8 +3256,8 @@
       <c r="E44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F44" s="3">
-        <v>2900</v>
+      <c r="F44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G44" s="3">
         <v>2900</v>
@@ -3177,7 +3272,7 @@
         <v>2900</v>
       </c>
       <c r="K44" s="3">
-        <v>0</v>
+        <v>2900</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -3227,35 +3322,38 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>2400</v>
+      <c r="D45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E45" s="3">
         <v>2400</v>
       </c>
       <c r="F45" s="3">
+        <v>2400</v>
+      </c>
+      <c r="G45" s="3">
         <v>2200</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I45" s="3">
         <v>1900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1600</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
       <c r="L45" s="3">
         <v>0</v>
       </c>
@@ -3304,35 +3402,38 @@
       <c r="AA45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>41400</v>
+      </c>
+      <c r="E46" s="3">
         <v>54700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>52800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>66400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>52900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>66300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>87500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>141400</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -3381,35 +3482,38 @@
       <c r="AA46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>70000</v>
+      </c>
+      <c r="E47" s="3">
         <v>86800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>87000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>87900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>88200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>87100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>85600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>88300</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
       <c r="L47" s="3">
         <v>0</v>
       </c>
@@ -3458,85 +3562,91 @@
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E48" s="3">
         <v>3500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>5500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4100</v>
-      </c>
-      <c r="M48" s="3">
-        <v>4000</v>
       </c>
       <c r="N48" s="3">
         <v>4000</v>
       </c>
       <c r="O48" s="3">
+        <v>4000</v>
+      </c>
+      <c r="P48" s="3">
         <v>3800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>7400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>7500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>7600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>8600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>8800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>8900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>9500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>8500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>8600</v>
-      </c>
-      <c r="Y48" s="3">
-        <v>8800</v>
       </c>
       <c r="Z48" s="3">
         <v>8800</v>
       </c>
       <c r="AA48" s="3">
+        <v>8800</v>
+      </c>
+      <c r="AB48" s="3">
         <v>8900</v>
       </c>
     </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3544,31 +3654,31 @@
         <v>18200</v>
       </c>
       <c r="E49" s="3">
-        <v>18300</v>
+        <v>18200</v>
       </c>
       <c r="F49" s="3">
         <v>18300</v>
       </c>
       <c r="G49" s="3">
-        <v>18400</v>
+        <v>18300</v>
       </c>
       <c r="H49" s="3">
         <v>18400</v>
       </c>
       <c r="I49" s="3">
-        <v>18500</v>
+        <v>18400</v>
       </c>
       <c r="J49" s="3">
         <v>18500</v>
       </c>
       <c r="K49" s="3">
-        <v>18600</v>
+        <v>18500</v>
       </c>
       <c r="L49" s="3">
         <v>18600</v>
       </c>
       <c r="M49" s="3">
-        <v>18700</v>
+        <v>18600</v>
       </c>
       <c r="N49" s="3">
         <v>18700</v>
@@ -3577,29 +3687,29 @@
         <v>18700</v>
       </c>
       <c r="P49" s="3">
-        <v>18800</v>
+        <v>18700</v>
       </c>
       <c r="Q49" s="3">
         <v>18800</v>
       </c>
       <c r="R49" s="3">
-        <v>18900</v>
+        <v>18800</v>
       </c>
       <c r="S49" s="3">
         <v>18900</v>
       </c>
       <c r="T49" s="3">
-        <v>19000</v>
+        <v>18900</v>
       </c>
       <c r="U49" s="3">
         <v>19000</v>
       </c>
       <c r="V49" s="3">
+        <v>19000</v>
+      </c>
+      <c r="W49" s="3">
         <v>19100</v>
       </c>
-      <c r="W49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X49" s="3" t="s">
         <v>5</v>
       </c>
@@ -3612,8 +3722,11 @@
       <c r="AA49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3689,8 +3802,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3766,35 +3882,38 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>28400</v>
+      </c>
+      <c r="E52" s="3">
         <v>26200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>27800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>27200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>27300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>28000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>27400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>27800</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
       <c r="L52" s="3">
         <v>0</v>
       </c>
@@ -3843,8 +3962,11 @@
       <c r="AA52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3920,85 +4042,91 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>866800</v>
+      </c>
+      <c r="E54" s="3">
         <v>878600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>873600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>869500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>843300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>855400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>876900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>932300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>791300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>776400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>766700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>760200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>788100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>790000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>786800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>797300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>850600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>888200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>906400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>642800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>319300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>309700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>305100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>308000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>307700</v>
       </c>
     </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4026,8 +4154,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4055,112 +4184,116 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>673500</v>
+      </c>
+      <c r="E57" s="3">
         <v>683800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>689700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>687400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>674400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>709000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>731000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>750800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>7000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>6000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>8200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>7800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>4700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>7600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>5300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>4600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>4100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>5300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>4700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>4500</v>
       </c>
     </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>58800</v>
+      </c>
+      <c r="E58" s="3">
         <v>4800</v>
       </c>
-      <c r="E58" s="3">
-        <v>0</v>
-      </c>
       <c r="F58" s="3">
         <v>0</v>
       </c>
       <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
         <v>600</v>
       </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
       <c r="I58" s="3">
         <v>0</v>
       </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
         <v>15000</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -4209,8 +4342,11 @@
       <c r="AA58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4235,8 +4371,8 @@
       <c r="J59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K59" s="3">
-        <v>0</v>
+      <c r="K59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L59" s="3">
         <v>0</v>
@@ -4286,35 +4422,38 @@
       <c r="AA59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>737700</v>
+      </c>
+      <c r="E60" s="3">
         <v>695400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>696700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>694400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>678100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>717000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>739000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>774000</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -4363,35 +4502,38 @@
       <c r="AA60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
         <v>54000</v>
-      </c>
-      <c r="E61" s="3">
-        <v>51800</v>
       </c>
       <c r="F61" s="3">
         <v>51800</v>
       </c>
       <c r="G61" s="3">
+        <v>51800</v>
+      </c>
+      <c r="H61" s="3">
         <v>41500</v>
-      </c>
-      <c r="H61" s="3">
-        <v>20000</v>
       </c>
       <c r="I61" s="3">
         <v>20000</v>
       </c>
       <c r="J61" s="3">
+        <v>20000</v>
+      </c>
+      <c r="K61" s="3">
         <v>40000</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -4414,17 +4556,17 @@
         <v>0</v>
       </c>
       <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3">
         <v>105800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>130000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>129200</v>
       </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
       <c r="W61" s="3">
         <v>0</v>
       </c>
@@ -4440,34 +4582,37 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E62" s="3">
         <v>700</v>
       </c>
-      <c r="E62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G62" s="3">
+      <c r="G62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H62" s="3">
         <v>1600</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I62" s="3" t="s">
         <v>5</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
+      <c r="K62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L62" s="3">
         <v>0</v>
@@ -4517,8 +4662,11 @@
       <c r="AA62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4594,8 +4742,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4671,8 +4822,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4748,85 +4902,91 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>737700</v>
+      </c>
+      <c r="E66" s="3">
         <v>750200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>748500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>746200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>721700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>737000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>759000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>814000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>674200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>661200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>651300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>643900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>667100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>670300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>669200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>682000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>769800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>809000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>829100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>566900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>242100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>233200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>228300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>231700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>231300</v>
       </c>
     </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4854,8 +5014,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4931,8 +5092,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5008,8 +5172,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5085,8 +5252,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5162,85 +5332,91 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>76800</v>
+      </c>
+      <c r="E72" s="3">
         <v>75400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>73700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>72700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>71300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>69800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>68200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>66600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>65400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>63700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>61800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>60000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>58200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>56900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>55100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>52800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>50700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>49200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>47300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>46300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>47600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>47100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>47300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>47200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>47000</v>
       </c>
     </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5316,8 +5492,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5393,8 +5572,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5470,85 +5652,91 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>129100</v>
+      </c>
+      <c r="E76" s="3">
         <v>128400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>125100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>123300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>121500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>118500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>117900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>118300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>117100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>115200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>115400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>116400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>121000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>119700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>117600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>115300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>80800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>79200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>77200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>75900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>77200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>76500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>76800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>76300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>76400</v>
       </c>
     </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5624,158 +5812,164 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E81" s="3">
         <v>1700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1500</v>
-      </c>
-      <c r="H81" s="3">
-        <v>1600</v>
       </c>
       <c r="I81" s="3">
         <v>1600</v>
       </c>
       <c r="J81" s="3">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="K81" s="3">
         <v>1700</v>
       </c>
       <c r="L81" s="3">
+        <v>1700</v>
+      </c>
+      <c r="M81" s="3">
         <v>1900</v>
-      </c>
-      <c r="M81" s="3">
-        <v>1800</v>
       </c>
       <c r="N81" s="3">
         <v>1800</v>
       </c>
       <c r="O81" s="3">
+        <v>1800</v>
+      </c>
+      <c r="P81" s="3">
         <v>1300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-1300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-200</v>
-      </c>
-      <c r="Y81" s="3">
-        <v>100</v>
       </c>
       <c r="Z81" s="3">
         <v>100</v>
@@ -5783,8 +5977,11 @@
       <c r="AA81" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB81" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5812,35 +6009,36 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>200</v>
+      </c>
+      <c r="E83" s="3">
         <v>100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>-900</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L83" s="3" t="s">
         <v>5</v>
       </c>
@@ -5853,18 +6051,18 @@
       <c r="O83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P83" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R83" s="3">
+      <c r="P83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q83" s="3">
+        <v>0</v>
+      </c>
+      <c r="R83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S83" s="3">
         <v>200</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T83" s="3" t="s">
         <v>5</v>
       </c>
@@ -5874,14 +6072,14 @@
       <c r="V83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W83" s="3">
+      <c r="W83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X83" s="3">
         <v>200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>300</v>
-      </c>
-      <c r="Y83" s="3">
-        <v>200</v>
       </c>
       <c r="Z83" s="3">
         <v>200</v>
@@ -5889,8 +6087,11 @@
       <c r="AA83" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5966,8 +6167,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6043,8 +6247,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6120,8 +6327,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6197,8 +6407,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6274,85 +6487,91 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E89" s="3">
         <v>4100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>3900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>3800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>8700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>2400</v>
       </c>
-      <c r="U89" s="3">
-        <v>0</v>
-      </c>
       <c r="V89" s="3">
+        <v>0</v>
+      </c>
+      <c r="W89" s="3">
         <v>-2900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6380,13 +6599,14 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>-100</v>
+      <c r="D91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E91" s="3">
         <v>-100</v>
@@ -6395,10 +6615,10 @@
         <v>-100</v>
       </c>
       <c r="G91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H91" s="3">
         <v>-200</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-100</v>
       </c>
       <c r="I91" s="3">
         <v>-100</v>
@@ -6407,58 +6627,61 @@
         <v>-100</v>
       </c>
       <c r="K91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L91" s="3">
         <v>-500</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-300</v>
       </c>
       <c r="M91" s="3">
         <v>-300</v>
       </c>
       <c r="N91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="O91" s="3">
         <v>-400</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-300</v>
       </c>
       <c r="P91" s="3">
         <v>-300</v>
       </c>
       <c r="Q91" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
         <v>-200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-100</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
       <c r="V91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W91" s="3">
         <v>-100</v>
       </c>
       <c r="X91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-100</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6534,8 +6757,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6611,85 +6837,91 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E94" s="3">
         <v>-3200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-13900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-14700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>1600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-29200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-26300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-26600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-23800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-17100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-17400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>11200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>23700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-27100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>33400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>5100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-115600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-33300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>13000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-7500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-7000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-4800</v>
       </c>
     </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6717,8 +6949,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6743,8 +6976,8 @@
       <c r="J96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -6794,8 +7027,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6871,8 +7107,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6948,8 +7187,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7025,85 +7267,91 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E100" s="3">
         <v>1000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>24800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-14900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-22300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-56600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>137800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>12800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>9300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>7300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-28700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>3300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-13200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-58400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-36600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-22300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>261700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>36400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>9100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>6000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7128,8 +7376,8 @@
       <c r="J101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -7179,81 +7427,87 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>1900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-11000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>11400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-11500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-21400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-54000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>110600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-14200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-14900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-14500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-41900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-19100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>15200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>14300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-76900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-14900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>146100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>10100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>18300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-11000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-6400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-3800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AFBI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AFBI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="92">
   <si>
     <t>AFBI</t>
   </si>
@@ -656,205 +656,212 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E8" s="3">
         <v>7400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>8000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>7900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>7300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>7400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>7500</v>
-      </c>
-      <c r="J8" s="3">
-        <v>7400</v>
       </c>
       <c r="K8" s="3">
         <v>7400</v>
       </c>
       <c r="L8" s="3">
+        <v>7400</v>
+      </c>
+      <c r="M8" s="3">
         <v>9000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>8200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>7600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>8300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>7400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>7600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>8200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>9200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>8000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>8700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>7300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>6700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3800</v>
-      </c>
-      <c r="AA8" s="3">
-        <v>3600</v>
       </c>
       <c r="AB8" s="3">
         <v>3600</v>
       </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC8" s="3">
+        <v>3600</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -933,37 +940,40 @@
       <c r="AB9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E10" s="3">
         <v>7400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>8000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>7900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>7300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>7400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>7500</v>
-      </c>
-      <c r="J10" s="3">
-        <v>7400</v>
       </c>
       <c r="K10" s="3">
         <v>7400</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>5</v>
+      <c r="L10" s="3">
+        <v>7400</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>5</v>
@@ -1013,8 +1023,11 @@
       <c r="AB10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1043,8 +1056,9 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1123,8 +1137,11 @@
       <c r="AB12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1203,8 +1220,11 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1232,8 +1252,8 @@
       <c r="K14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1283,8 +1303,11 @@
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1313,7 +1336,7 @@
         <v>200</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1363,8 +1386,11 @@
       <c r="AB15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1390,79 +1416,80 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E17" s="3">
         <v>5800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>5700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>6700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>5600</v>
-      </c>
-      <c r="H17" s="3">
-        <v>5400</v>
       </c>
       <c r="I17" s="3">
         <v>5400</v>
       </c>
       <c r="J17" s="3">
+        <v>5400</v>
+      </c>
+      <c r="K17" s="3">
         <v>5300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>700</v>
-      </c>
-      <c r="O17" s="3">
-        <v>800</v>
       </c>
       <c r="P17" s="3">
         <v>800</v>
       </c>
       <c r="Q17" s="3">
+        <v>800</v>
+      </c>
+      <c r="R17" s="3">
         <v>1000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1400</v>
-      </c>
-      <c r="V17" s="3">
-        <v>1500</v>
       </c>
       <c r="W17" s="3">
         <v>1500</v>
       </c>
       <c r="X17" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Y17" s="3">
         <v>700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>600</v>
-      </c>
-      <c r="Z17" s="3">
-        <v>500</v>
       </c>
       <c r="AA17" s="3">
         <v>500</v>
@@ -1470,88 +1497,94 @@
       <c r="AB17" s="3">
         <v>500</v>
       </c>
-    </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC17" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E18" s="3">
         <v>1600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1900</v>
-      </c>
-      <c r="I18" s="3">
-        <v>2100</v>
       </c>
       <c r="J18" s="3">
         <v>2100</v>
       </c>
       <c r="K18" s="3">
+        <v>2100</v>
+      </c>
+      <c r="L18" s="3">
         <v>2200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>7300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>7400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>6900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>7500</v>
-      </c>
-      <c r="P18" s="3">
-        <v>6600</v>
       </c>
       <c r="Q18" s="3">
         <v>6600</v>
       </c>
       <c r="R18" s="3">
+        <v>6600</v>
+      </c>
+      <c r="S18" s="3">
         <v>7100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>7800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>6900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>7300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>5800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>5200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>3100</v>
-      </c>
-      <c r="Y18" s="3">
-        <v>3300</v>
       </c>
       <c r="Z18" s="3">
         <v>3300</v>
       </c>
       <c r="AA18" s="3">
-        <v>3100</v>
+        <v>3300</v>
       </c>
       <c r="AB18" s="3">
         <v>3100</v>
       </c>
-    </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC18" s="3">
+        <v>3100</v>
+      </c>
+    </row>
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1580,23 +1613,24 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F20" s="3">
+      <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G20" s="3">
         <v>-100</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H20" s="3" t="s">
         <v>5</v>
       </c>
@@ -1609,89 +1643,92 @@
       <c r="K20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M20" s="3">
         <v>-5100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-4900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-4600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-5200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-4800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-4200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-4100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-5100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-5000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-4800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-4400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-7100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-2800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-3600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-3100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-3000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-2900</v>
       </c>
     </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E21" s="3">
         <v>1800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2100</v>
-      </c>
-      <c r="I21" s="3">
-        <v>2300</v>
       </c>
       <c r="J21" s="3">
         <v>2300</v>
       </c>
       <c r="K21" s="3">
+        <v>2300</v>
+      </c>
+      <c r="L21" s="3">
         <v>2400</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>5</v>
       </c>
@@ -1710,12 +1747,12 @@
       <c r="R21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T21" s="3">
         <v>2900</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>5</v>
       </c>
@@ -1725,14 +1762,14 @@
       <c r="W21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X21" s="3">
+      <c r="X21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y21" s="3">
         <v>600</v>
       </c>
-      <c r="Y21" s="3">
-        <v>0</v>
-      </c>
       <c r="Z21" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AA21" s="3">
         <v>300</v>
@@ -1740,8 +1777,11 @@
       <c r="AB21" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC21" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1769,8 +1809,8 @@
       <c r="K22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1820,108 +1860,114 @@
       <c r="AB22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E23" s="3">
         <v>1600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1900</v>
-      </c>
-      <c r="I23" s="3">
-        <v>2100</v>
       </c>
       <c r="J23" s="3">
         <v>2100</v>
       </c>
       <c r="K23" s="3">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="L23" s="3">
         <v>2200</v>
       </c>
       <c r="M23" s="3">
+        <v>2200</v>
+      </c>
+      <c r="N23" s="3">
         <v>2400</v>
-      </c>
-      <c r="N23" s="3">
-        <v>2300</v>
       </c>
       <c r="O23" s="3">
         <v>2300</v>
       </c>
       <c r="P23" s="3">
+        <v>2300</v>
+      </c>
+      <c r="Q23" s="3">
         <v>1800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>3000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>2400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-1800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-300</v>
-      </c>
-      <c r="Z23" s="3">
-        <v>100</v>
       </c>
       <c r="AA23" s="3">
         <v>100</v>
       </c>
       <c r="AB23" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC23" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>600</v>
+      </c>
+      <c r="E24" s="3">
         <v>300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>300</v>
-      </c>
-      <c r="G24" s="3">
-        <v>400</v>
       </c>
       <c r="H24" s="3">
         <v>400</v>
       </c>
       <c r="I24" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="J24" s="3">
         <v>500</v>
@@ -1933,55 +1979,58 @@
         <v>500</v>
       </c>
       <c r="M24" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="N24" s="3">
         <v>600</v>
       </c>
       <c r="O24" s="3">
+        <v>600</v>
+      </c>
+      <c r="P24" s="3">
         <v>500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-100</v>
       </c>
-      <c r="Z24" s="3">
-        <v>0</v>
-      </c>
       <c r="AA24" s="3">
         <v>0</v>
       </c>
       <c r="AB24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2060,79 +2109,82 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E26" s="3">
         <v>1300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1500</v>
-      </c>
-      <c r="I26" s="3">
-        <v>1600</v>
       </c>
       <c r="J26" s="3">
         <v>1600</v>
       </c>
       <c r="K26" s="3">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="L26" s="3">
         <v>1700</v>
       </c>
       <c r="M26" s="3">
+        <v>1700</v>
+      </c>
+      <c r="N26" s="3">
         <v>1900</v>
-      </c>
-      <c r="N26" s="3">
-        <v>1800</v>
       </c>
       <c r="O26" s="3">
         <v>1800</v>
       </c>
       <c r="P26" s="3">
+        <v>1800</v>
+      </c>
+      <c r="Q26" s="3">
         <v>1300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-1300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-200</v>
-      </c>
-      <c r="Z26" s="3">
-        <v>100</v>
       </c>
       <c r="AA26" s="3">
         <v>100</v>
@@ -2140,79 +2192,82 @@
       <c r="AB26" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC26" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E27" s="3">
         <v>1300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1500</v>
-      </c>
-      <c r="I27" s="3">
-        <v>1600</v>
       </c>
       <c r="J27" s="3">
         <v>1600</v>
       </c>
       <c r="K27" s="3">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="L27" s="3">
         <v>1700</v>
       </c>
       <c r="M27" s="3">
+        <v>1700</v>
+      </c>
+      <c r="N27" s="3">
         <v>1900</v>
-      </c>
-      <c r="N27" s="3">
-        <v>1800</v>
       </c>
       <c r="O27" s="3">
         <v>1800</v>
       </c>
       <c r="P27" s="3">
+        <v>1800</v>
+      </c>
+      <c r="Q27" s="3">
         <v>1300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-1300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-200</v>
-      </c>
-      <c r="Z27" s="3">
-        <v>100</v>
       </c>
       <c r="AA27" s="3">
         <v>100</v>
@@ -2220,8 +2275,11 @@
       <c r="AB27" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC27" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2300,8 +2358,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2362,8 +2423,8 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>5</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>5</v>
@@ -2380,8 +2441,11 @@
       <c r="AB29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2460,8 +2524,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2540,23 +2607,26 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F32" s="3">
+      <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G32" s="3">
         <v>100</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H32" s="3" t="s">
         <v>5</v>
       </c>
@@ -2569,130 +2639,133 @@
       <c r="K32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M32" s="3">
         <v>5100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>4900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>4600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>5200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>4800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>4200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>4100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>5100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>5000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>4800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>4400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>7100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>2800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>3600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>3100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>3000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E33" s="3">
         <v>1300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1500</v>
-      </c>
-      <c r="I33" s="3">
-        <v>1600</v>
       </c>
       <c r="J33" s="3">
         <v>1600</v>
       </c>
       <c r="K33" s="3">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="L33" s="3">
         <v>1700</v>
       </c>
       <c r="M33" s="3">
+        <v>1700</v>
+      </c>
+      <c r="N33" s="3">
         <v>1900</v>
-      </c>
-      <c r="N33" s="3">
-        <v>1800</v>
       </c>
       <c r="O33" s="3">
         <v>1800</v>
       </c>
       <c r="P33" s="3">
+        <v>1800</v>
+      </c>
+      <c r="Q33" s="3">
         <v>1300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-1300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-200</v>
-      </c>
-      <c r="Z33" s="3">
-        <v>100</v>
       </c>
       <c r="AA33" s="3">
         <v>100</v>
@@ -2700,8 +2773,11 @@
       <c r="AB33" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC33" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2780,79 +2856,82 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E35" s="3">
         <v>1300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1500</v>
-      </c>
-      <c r="I35" s="3">
-        <v>1600</v>
       </c>
       <c r="J35" s="3">
         <v>1600</v>
       </c>
       <c r="K35" s="3">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="L35" s="3">
         <v>1700</v>
       </c>
       <c r="M35" s="3">
+        <v>1700</v>
+      </c>
+      <c r="N35" s="3">
         <v>1900</v>
-      </c>
-      <c r="N35" s="3">
-        <v>1800</v>
       </c>
       <c r="O35" s="3">
         <v>1800</v>
       </c>
       <c r="P35" s="3">
+        <v>1800</v>
+      </c>
+      <c r="Q35" s="3">
         <v>1300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-1300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-200</v>
-      </c>
-      <c r="Z35" s="3">
-        <v>100</v>
       </c>
       <c r="AA35" s="3">
         <v>100</v>
@@ -2860,93 +2939,99 @@
       <c r="AB35" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC35" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2975,8 +3060,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3005,88 +3091,92 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>74700</v>
+      </c>
+      <c r="E41" s="3">
         <v>41400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>52300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>50400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>61400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>50000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>61500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>82900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>136900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>8100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>14300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>16200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>17300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>15300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>10000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>5600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>6200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>14300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>6400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>4000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>3300</v>
-      </c>
-      <c r="Z41" s="3">
-        <v>4600</v>
       </c>
       <c r="AA41" s="3">
         <v>4600</v>
       </c>
       <c r="AB41" s="3">
+        <v>4600</v>
+      </c>
+      <c r="AC41" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3115,58 +3205,61 @@
         <v>0</v>
       </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>37000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>43900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>57700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>66100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>107300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>122700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>109000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>97600</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>176900</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>178200</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>185600</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>47200</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>44400</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>35000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>15400</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>26300</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>33800</v>
       </c>
     </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3194,8 +3287,8 @@
       <c r="K43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
+      <c r="L43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
@@ -3245,8 +3338,11 @@
       <c r="AB43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3259,8 +3355,8 @@
       <c r="F44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G44" s="3">
-        <v>2900</v>
+      <c r="G44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H44" s="3">
         <v>2900</v>
@@ -3275,7 +3371,7 @@
         <v>2900</v>
       </c>
       <c r="L44" s="3">
-        <v>0</v>
+        <v>2900</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -3325,38 +3421,41 @@
       <c r="AB44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>5</v>
+      <c r="D45" s="3">
+        <v>2300</v>
       </c>
       <c r="E45" s="3">
-        <v>2400</v>
+        <v>2300</v>
       </c>
       <c r="F45" s="3">
         <v>2400</v>
       </c>
       <c r="G45" s="3">
+        <v>2400</v>
+      </c>
+      <c r="H45" s="3">
         <v>2200</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I45" s="3">
+        <v>2100</v>
+      </c>
+      <c r="J45" s="3">
         <v>1900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1600</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
       <c r="M45" s="3">
         <v>0</v>
       </c>
@@ -3405,38 +3504,41 @@
       <c r="AB45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>41400</v>
+        <v>77000</v>
       </c>
       <c r="E46" s="3">
+        <v>43700</v>
+      </c>
+      <c r="F46" s="3">
         <v>54700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>52800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>66400</v>
       </c>
-      <c r="H46" s="3">
-        <v>52900</v>
-      </c>
       <c r="I46" s="3">
+        <v>55000</v>
+      </c>
+      <c r="J46" s="3">
         <v>66300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>87500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>141400</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -3485,38 +3587,41 @@
       <c r="AB46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>74500</v>
+      </c>
+      <c r="E47" s="3">
         <v>70000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>86800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>87000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>87900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>88200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>87100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>85600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>88300</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
       <c r="M47" s="3">
         <v>0</v>
       </c>
@@ -3565,123 +3670,129 @@
       <c r="AB47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>3300</v>
+        <v>3200</v>
       </c>
       <c r="E48" s="3">
+        <v>4500</v>
+      </c>
+      <c r="F48" s="3">
         <v>3500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>5500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4100</v>
-      </c>
-      <c r="N48" s="3">
-        <v>4000</v>
       </c>
       <c r="O48" s="3">
         <v>4000</v>
       </c>
       <c r="P48" s="3">
+        <v>4000</v>
+      </c>
+      <c r="Q48" s="3">
         <v>3800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>7400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>7500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>7600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>8600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>8800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>8900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>9500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>8500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>8600</v>
-      </c>
-      <c r="Z48" s="3">
-        <v>8800</v>
       </c>
       <c r="AA48" s="3">
         <v>8800</v>
       </c>
       <c r="AB48" s="3">
+        <v>8800</v>
+      </c>
+      <c r="AC48" s="3">
         <v>8900</v>
       </c>
     </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>18200</v>
+        <v>18100</v>
       </c>
       <c r="E49" s="3">
         <v>18200</v>
       </c>
       <c r="F49" s="3">
-        <v>18300</v>
+        <v>18200</v>
       </c>
       <c r="G49" s="3">
         <v>18300</v>
       </c>
       <c r="H49" s="3">
-        <v>18400</v>
+        <v>18300</v>
       </c>
       <c r="I49" s="3">
         <v>18400</v>
       </c>
       <c r="J49" s="3">
-        <v>18500</v>
+        <v>18400</v>
       </c>
       <c r="K49" s="3">
         <v>18500</v>
       </c>
       <c r="L49" s="3">
-        <v>18600</v>
+        <v>18500</v>
       </c>
       <c r="M49" s="3">
         <v>18600</v>
       </c>
       <c r="N49" s="3">
-        <v>18700</v>
+        <v>18600</v>
       </c>
       <c r="O49" s="3">
         <v>18700</v>
@@ -3690,29 +3801,29 @@
         <v>18700</v>
       </c>
       <c r="Q49" s="3">
-        <v>18800</v>
+        <v>18700</v>
       </c>
       <c r="R49" s="3">
         <v>18800</v>
       </c>
       <c r="S49" s="3">
-        <v>18900</v>
+        <v>18800</v>
       </c>
       <c r="T49" s="3">
         <v>18900</v>
       </c>
       <c r="U49" s="3">
-        <v>19000</v>
+        <v>18900</v>
       </c>
       <c r="V49" s="3">
         <v>19000</v>
       </c>
       <c r="W49" s="3">
+        <v>19000</v>
+      </c>
+      <c r="X49" s="3">
         <v>19100</v>
       </c>
-      <c r="X49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y49" s="3" t="s">
         <v>5</v>
       </c>
@@ -3725,8 +3836,11 @@
       <c r="AB49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3805,8 +3919,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3885,38 +4002,41 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>28400</v>
+        <v>27100</v>
       </c>
       <c r="E52" s="3">
+        <v>24800</v>
+      </c>
+      <c r="F52" s="3">
         <v>26200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>27800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>27200</v>
       </c>
-      <c r="H52" s="3">
-        <v>27300</v>
-      </c>
       <c r="I52" s="3">
+        <v>25200</v>
+      </c>
+      <c r="J52" s="3">
         <v>28000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>27400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>27800</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
-      </c>
       <c r="M52" s="3">
         <v>0</v>
       </c>
@@ -3965,8 +4085,11 @@
       <c r="AB52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4045,88 +4168,94 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>912500</v>
+      </c>
+      <c r="E54" s="3">
         <v>866800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>878600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>873600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>869500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>843300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>855400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>876900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>932300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>791300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>776400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>766700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>760200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>788100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>790000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>786800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>797300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>850600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>888200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>906400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>642800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>319300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>309700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>305100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>308000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>307700</v>
       </c>
     </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4155,8 +4284,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4185,105 +4315,109 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>730300</v>
+      </c>
+      <c r="E57" s="3">
         <v>673500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>683800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>689700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>687400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>674400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>709000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>731000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>750800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>7000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>6000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>8200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>7800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>4700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>7600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>5300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>4600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>3900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>4100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>5300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>4700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>4500</v>
       </c>
     </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>58800</v>
+        <v>0</v>
       </c>
       <c r="E58" s="3">
+        <v>5400</v>
+      </c>
+      <c r="F58" s="3">
         <v>4800</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
       <c r="G58" s="3">
         <v>0</v>
       </c>
       <c r="H58" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="I58" s="3">
         <v>0</v>
@@ -4292,11 +4426,11 @@
         <v>0</v>
       </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>15000</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -4345,8 +4479,11 @@
       <c r="AB58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4374,8 +4511,8 @@
       <c r="K59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L59" s="3">
-        <v>0</v>
+      <c r="L59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M59" s="3">
         <v>0</v>
@@ -4425,38 +4562,41 @@
       <c r="AB59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>737700</v>
+        <v>736200</v>
       </c>
       <c r="E60" s="3">
+        <v>681100</v>
+      </c>
+      <c r="F60" s="3">
         <v>695400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>696700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>694400</v>
       </c>
-      <c r="H60" s="3">
-        <v>678100</v>
-      </c>
       <c r="I60" s="3">
+        <v>677500</v>
+      </c>
+      <c r="J60" s="3">
         <v>717000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>739000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>774000</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -4505,38 +4645,41 @@
       <c r="AB60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>54000</v>
       </c>
       <c r="E61" s="3">
+        <v>55000</v>
+      </c>
+      <c r="F61" s="3">
         <v>54000</v>
-      </c>
-      <c r="F61" s="3">
-        <v>51800</v>
       </c>
       <c r="G61" s="3">
         <v>51800</v>
       </c>
       <c r="H61" s="3">
-        <v>41500</v>
+        <v>51800</v>
       </c>
       <c r="I61" s="3">
-        <v>20000</v>
+        <v>42200</v>
       </c>
       <c r="J61" s="3">
         <v>20000</v>
       </c>
       <c r="K61" s="3">
+        <v>20000</v>
+      </c>
+      <c r="L61" s="3">
         <v>40000</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -4559,17 +4702,17 @@
         <v>0</v>
       </c>
       <c r="T61" s="3">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3">
         <v>105800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>130000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>129200</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
       <c r="X61" s="3">
         <v>0</v>
       </c>
@@ -4585,8 +4728,11 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4594,28 +4740,28 @@
         <v>5</v>
       </c>
       <c r="E62" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F62" s="3">
         <v>700</v>
       </c>
-      <c r="F62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H62" s="3">
+      <c r="H62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I62" s="3">
         <v>1600</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J62" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
+      <c r="L62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M62" s="3">
         <v>0</v>
@@ -4665,8 +4811,11 @@
       <c r="AB62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4745,8 +4894,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4825,8 +4977,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4905,88 +5060,94 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>790200</v>
+      </c>
+      <c r="E66" s="3">
         <v>737700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>750200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>748500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>746200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>721700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>737000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>759000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>814000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>674200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>661200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>651300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>643900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>667100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>670300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>669200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>682000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>769800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>809000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>829100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>566900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>242100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>233200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>228300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>231700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>231300</v>
       </c>
     </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5015,8 +5176,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5095,8 +5257,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5175,8 +5340,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5255,8 +5423,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5335,88 +5506,94 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>69600</v>
+      </c>
+      <c r="E72" s="3">
         <v>76800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>75400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>73700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>72700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>71300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>69800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>68200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>66600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>65400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>63700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>61800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>60000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>58200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>56900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>55100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>52800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>50700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>49200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>47300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>46300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>47600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>47100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>47300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>47200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>47000</v>
       </c>
     </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5495,8 +5672,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5575,8 +5755,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5655,88 +5838,94 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>122300</v>
+      </c>
+      <c r="E76" s="3">
         <v>129100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>128400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>125100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>123300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>121500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>118500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>117900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>118300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>117100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>115200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>115400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>116400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>121000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>119700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>117600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>115300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>80800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>79200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>77200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>75900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>77200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>76500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>76800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>76300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>76400</v>
       </c>
     </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5815,164 +6004,170 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E81" s="3">
         <v>1300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1500</v>
-      </c>
-      <c r="I81" s="3">
-        <v>1600</v>
       </c>
       <c r="J81" s="3">
         <v>1600</v>
       </c>
       <c r="K81" s="3">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="L81" s="3">
         <v>1700</v>
       </c>
       <c r="M81" s="3">
+        <v>1700</v>
+      </c>
+      <c r="N81" s="3">
         <v>1900</v>
-      </c>
-      <c r="N81" s="3">
-        <v>1800</v>
       </c>
       <c r="O81" s="3">
         <v>1800</v>
       </c>
       <c r="P81" s="3">
+        <v>1800</v>
+      </c>
+      <c r="Q81" s="3">
         <v>1300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-1300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-200</v>
-      </c>
-      <c r="Z81" s="3">
-        <v>100</v>
       </c>
       <c r="AA81" s="3">
         <v>100</v>
@@ -5980,8 +6175,11 @@
       <c r="AB81" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC81" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6010,38 +6208,39 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E83" s="3">
         <v>100</v>
       </c>
       <c r="F83" s="3">
+        <v>100</v>
+      </c>
+      <c r="G83" s="3">
         <v>200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>100</v>
       </c>
-      <c r="H83" s="3">
-        <v>700</v>
-      </c>
       <c r="I83" s="3">
+        <v>500</v>
+      </c>
+      <c r="J83" s="3">
         <v>300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>-900</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M83" s="3" t="s">
         <v>5</v>
       </c>
@@ -6054,18 +6253,18 @@
       <c r="P83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
-      </c>
-      <c r="R83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S83" s="3">
+      <c r="Q83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R83" s="3">
+        <v>0</v>
+      </c>
+      <c r="S83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T83" s="3">
         <v>200</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U83" s="3" t="s">
         <v>5</v>
       </c>
@@ -6075,14 +6274,14 @@
       <c r="W83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X83" s="3">
+      <c r="X83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y83" s="3">
         <v>200</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>300</v>
-      </c>
-      <c r="Z83" s="3">
-        <v>200</v>
       </c>
       <c r="AA83" s="3">
         <v>200</v>
@@ -6090,8 +6289,11 @@
       <c r="AB83" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6170,8 +6372,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6250,8 +6455,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6330,8 +6538,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6410,8 +6621,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6490,88 +6704,94 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>5</v>
+      <c r="D89" s="3">
+        <v>1900</v>
       </c>
       <c r="E89" s="3">
+        <v>900</v>
+      </c>
+      <c r="F89" s="3">
         <v>4100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>3900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>3800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>8700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>2400</v>
       </c>
-      <c r="V89" s="3">
-        <v>0</v>
-      </c>
       <c r="W89" s="3">
+        <v>0</v>
+      </c>
+      <c r="X89" s="3">
         <v>-2900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6600,16 +6820,17 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>5</v>
+      <c r="D91" s="3">
+        <v>-100</v>
       </c>
       <c r="E91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F91" s="3">
         <v>-100</v>
@@ -6618,10 +6839,10 @@
         <v>-100</v>
       </c>
       <c r="H91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I91" s="3">
         <v>-200</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-100</v>
       </c>
       <c r="J91" s="3">
         <v>-100</v>
@@ -6630,58 +6851,61 @@
         <v>-100</v>
       </c>
       <c r="L91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M91" s="3">
         <v>-500</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-300</v>
       </c>
       <c r="N91" s="3">
         <v>-300</v>
       </c>
       <c r="O91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="P91" s="3">
         <v>-400</v>
-      </c>
-      <c r="P91" s="3">
-        <v>-300</v>
       </c>
       <c r="Q91" s="3">
         <v>-300</v>
       </c>
       <c r="R91" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
         <v>-200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-100</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
       <c r="W91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="X91" s="3">
         <v>-100</v>
       </c>
       <c r="Y91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-100</v>
       </c>
-      <c r="AB91" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6760,8 +6984,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6840,88 +7067,94 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>5</v>
+      <c r="D94" s="3">
+        <v>-10700</v>
       </c>
       <c r="E94" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="F94" s="3">
         <v>-3200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-13900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-14700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>1600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-29200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-26300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-26600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-23800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-17100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-17400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>11200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>23700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-27100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>33400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>5100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-115600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-33300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>13000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-7500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-7000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-4800</v>
       </c>
     </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6950,13 +7183,14 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>5</v>
+      <c r="D96" s="3">
+        <v>8800</v>
       </c>
       <c r="E96" s="3" t="s">
         <v>5</v>
@@ -6979,8 +7213,8 @@
       <c r="K96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -7030,8 +7264,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7110,8 +7347,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7190,8 +7430,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7270,88 +7513,94 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>5</v>
+      <c r="D100" s="3">
+        <v>42100</v>
       </c>
       <c r="E100" s="3">
+        <v>-10300</v>
+      </c>
+      <c r="F100" s="3">
         <v>1000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>24800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-14900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-22300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-56600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>137800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>12800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>9300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>7300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-28700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>3300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-13200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-58400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-36600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-22300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>261700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>36400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>9100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>6000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-3900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7379,8 +7628,8 @@
       <c r="K101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -7430,84 +7679,90 @@
       <c r="AB101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>33300</v>
       </c>
       <c r="E102" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="F102" s="3">
         <v>1900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-11000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>11400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-11500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-21400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-54000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>110600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-14200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-14900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-14500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-41900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-19100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>15200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>14300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-76900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-14900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>146100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>10100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>18300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-11000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-6400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-3800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AFBI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AFBI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="92">
   <si>
     <t>AFBI</t>
   </si>
@@ -656,212 +656,219 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E8" s="3">
         <v>7800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>7400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>8000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>7900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>7300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>7400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>7500</v>
-      </c>
-      <c r="K8" s="3">
-        <v>7400</v>
       </c>
       <c r="L8" s="3">
         <v>7400</v>
       </c>
       <c r="M8" s="3">
+        <v>7400</v>
+      </c>
+      <c r="N8" s="3">
         <v>9000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>8200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>7600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>8300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>7400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>7600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>8200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>9200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>8000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>8700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>7300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>6700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3800</v>
-      </c>
-      <c r="AB8" s="3">
-        <v>3600</v>
       </c>
       <c r="AC8" s="3">
         <v>3600</v>
       </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD8" s="3">
+        <v>3600</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -943,40 +950,43 @@
       <c r="AC9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E10" s="3">
         <v>7800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>7400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>8000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>7900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>7300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>7400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>7500</v>
-      </c>
-      <c r="K10" s="3">
-        <v>7400</v>
       </c>
       <c r="L10" s="3">
         <v>7400</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>5</v>
+      <c r="M10" s="3">
+        <v>7400</v>
       </c>
       <c r="N10" s="3" t="s">
         <v>5</v>
@@ -1026,8 +1036,11 @@
       <c r="AC10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1057,8 +1070,9 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1140,8 +1154,11 @@
       <c r="AC12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1223,8 +1240,11 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1255,8 +1275,8 @@
       <c r="L14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1306,8 +1326,11 @@
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1339,7 +1362,7 @@
         <v>200</v>
       </c>
       <c r="M15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
@@ -1389,8 +1412,11 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1417,82 +1443,83 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E17" s="3">
         <v>5400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>5800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>5700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>6700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>5600</v>
-      </c>
-      <c r="I17" s="3">
-        <v>5400</v>
       </c>
       <c r="J17" s="3">
         <v>5400</v>
       </c>
       <c r="K17" s="3">
+        <v>5400</v>
+      </c>
+      <c r="L17" s="3">
         <v>5300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>700</v>
-      </c>
-      <c r="P17" s="3">
-        <v>800</v>
       </c>
       <c r="Q17" s="3">
         <v>800</v>
       </c>
       <c r="R17" s="3">
+        <v>800</v>
+      </c>
+      <c r="S17" s="3">
         <v>1000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1400</v>
-      </c>
-      <c r="W17" s="3">
-        <v>1500</v>
       </c>
       <c r="X17" s="3">
         <v>1500</v>
       </c>
       <c r="Y17" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Z17" s="3">
         <v>700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>600</v>
-      </c>
-      <c r="AA17" s="3">
-        <v>500</v>
       </c>
       <c r="AB17" s="3">
         <v>500</v>
@@ -1500,91 +1527,97 @@
       <c r="AC17" s="3">
         <v>500</v>
       </c>
-    </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD17" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E18" s="3">
         <v>2400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1900</v>
-      </c>
-      <c r="J18" s="3">
-        <v>2100</v>
       </c>
       <c r="K18" s="3">
         <v>2100</v>
       </c>
       <c r="L18" s="3">
+        <v>2100</v>
+      </c>
+      <c r="M18" s="3">
         <v>2200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>7300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>7400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>6900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>7500</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>6600</v>
       </c>
       <c r="R18" s="3">
         <v>6600</v>
       </c>
       <c r="S18" s="3">
+        <v>6600</v>
+      </c>
+      <c r="T18" s="3">
         <v>7100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>7800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>6900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>7300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>5800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>5200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>3100</v>
-      </c>
-      <c r="Z18" s="3">
-        <v>3300</v>
       </c>
       <c r="AA18" s="3">
         <v>3300</v>
       </c>
       <c r="AB18" s="3">
-        <v>3100</v>
+        <v>3300</v>
       </c>
       <c r="AC18" s="3">
         <v>3100</v>
       </c>
-    </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD18" s="3">
+        <v>3100</v>
+      </c>
+    </row>
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1614,26 +1647,27 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G20" s="3">
+      <c r="E20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H20" s="3">
         <v>-100</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I20" s="3" t="s">
         <v>5</v>
       </c>
@@ -1646,92 +1680,95 @@
       <c r="L20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N20" s="3">
         <v>-5100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-4900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-4600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-5200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-4800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-4200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-4100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-5100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-5000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-4800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-4400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-7100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-2800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-3100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-3000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-2900</v>
       </c>
     </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E21" s="3">
         <v>2600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2100</v>
-      </c>
-      <c r="J21" s="3">
-        <v>2300</v>
       </c>
       <c r="K21" s="3">
         <v>2300</v>
       </c>
       <c r="L21" s="3">
+        <v>2300</v>
+      </c>
+      <c r="M21" s="3">
         <v>2400</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>5</v>
       </c>
@@ -1750,12 +1787,12 @@
       <c r="S21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T21" s="3">
+      <c r="T21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U21" s="3">
         <v>2900</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>5</v>
       </c>
@@ -1765,14 +1802,14 @@
       <c r="X21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Y21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z21" s="3">
         <v>600</v>
       </c>
-      <c r="Z21" s="3">
-        <v>0</v>
-      </c>
       <c r="AA21" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AB21" s="3">
         <v>300</v>
@@ -1780,8 +1817,11 @@
       <c r="AC21" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD21" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1812,8 +1852,8 @@
       <c r="L22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1863,114 +1903,120 @@
       <c r="AC22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E23" s="3">
         <v>2400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1900</v>
-      </c>
-      <c r="J23" s="3">
-        <v>2100</v>
       </c>
       <c r="K23" s="3">
         <v>2100</v>
       </c>
       <c r="L23" s="3">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="M23" s="3">
         <v>2200</v>
       </c>
       <c r="N23" s="3">
+        <v>2200</v>
+      </c>
+      <c r="O23" s="3">
         <v>2400</v>
-      </c>
-      <c r="O23" s="3">
-        <v>2300</v>
       </c>
       <c r="P23" s="3">
         <v>2300</v>
       </c>
       <c r="Q23" s="3">
+        <v>2300</v>
+      </c>
+      <c r="R23" s="3">
         <v>1800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>3000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>2400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-300</v>
-      </c>
-      <c r="AA23" s="3">
-        <v>100</v>
       </c>
       <c r="AB23" s="3">
         <v>100</v>
       </c>
       <c r="AC23" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD23" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>700</v>
+      </c>
+      <c r="E24" s="3">
         <v>600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>300</v>
-      </c>
-      <c r="H24" s="3">
-        <v>400</v>
       </c>
       <c r="I24" s="3">
         <v>400</v>
       </c>
       <c r="J24" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="K24" s="3">
         <v>500</v>
@@ -1982,55 +2028,58 @@
         <v>500</v>
       </c>
       <c r="N24" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="O24" s="3">
         <v>600</v>
       </c>
       <c r="P24" s="3">
+        <v>600</v>
+      </c>
+      <c r="Q24" s="3">
         <v>500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-100</v>
       </c>
-      <c r="AA24" s="3">
-        <v>0</v>
-      </c>
       <c r="AB24" s="3">
         <v>0</v>
       </c>
       <c r="AC24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2112,82 +2161,85 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E26" s="3">
         <v>1800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1500</v>
-      </c>
-      <c r="J26" s="3">
-        <v>1600</v>
       </c>
       <c r="K26" s="3">
         <v>1600</v>
       </c>
       <c r="L26" s="3">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="M26" s="3">
         <v>1700</v>
       </c>
       <c r="N26" s="3">
+        <v>1700</v>
+      </c>
+      <c r="O26" s="3">
         <v>1900</v>
-      </c>
-      <c r="O26" s="3">
-        <v>1800</v>
       </c>
       <c r="P26" s="3">
         <v>1800</v>
       </c>
       <c r="Q26" s="3">
+        <v>1800</v>
+      </c>
+      <c r="R26" s="3">
         <v>1300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-200</v>
-      </c>
-      <c r="AA26" s="3">
-        <v>100</v>
       </c>
       <c r="AB26" s="3">
         <v>100</v>
@@ -2195,82 +2247,85 @@
       <c r="AC26" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD26" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E27" s="3">
         <v>1800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1500</v>
-      </c>
-      <c r="J27" s="3">
-        <v>1600</v>
       </c>
       <c r="K27" s="3">
         <v>1600</v>
       </c>
       <c r="L27" s="3">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="M27" s="3">
         <v>1700</v>
       </c>
       <c r="N27" s="3">
+        <v>1700</v>
+      </c>
+      <c r="O27" s="3">
         <v>1900</v>
-      </c>
-      <c r="O27" s="3">
-        <v>1800</v>
       </c>
       <c r="P27" s="3">
         <v>1800</v>
       </c>
       <c r="Q27" s="3">
+        <v>1800</v>
+      </c>
+      <c r="R27" s="3">
         <v>1300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-200</v>
-      </c>
-      <c r="AA27" s="3">
-        <v>100</v>
       </c>
       <c r="AB27" s="3">
         <v>100</v>
@@ -2278,8 +2333,11 @@
       <c r="AC27" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD27" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2361,8 +2419,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2426,8 +2487,8 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>5</v>
+      <c r="X29" s="3">
+        <v>0</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>5</v>
@@ -2444,8 +2505,11 @@
       <c r="AC29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2527,8 +2591,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2610,26 +2677,29 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G32" s="3">
+      <c r="E32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H32" s="3">
         <v>100</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I32" s="3" t="s">
         <v>5</v>
       </c>
@@ -2642,133 +2712,136 @@
       <c r="L32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N32" s="3">
         <v>5100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>4900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>4600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>5200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>4800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>4200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>4100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>5100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>5000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>4800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>4400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>7100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>2800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>3600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>3100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>3000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E33" s="3">
         <v>1800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1500</v>
-      </c>
-      <c r="J33" s="3">
-        <v>1600</v>
       </c>
       <c r="K33" s="3">
         <v>1600</v>
       </c>
       <c r="L33" s="3">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="M33" s="3">
         <v>1700</v>
       </c>
       <c r="N33" s="3">
+        <v>1700</v>
+      </c>
+      <c r="O33" s="3">
         <v>1900</v>
-      </c>
-      <c r="O33" s="3">
-        <v>1800</v>
       </c>
       <c r="P33" s="3">
         <v>1800</v>
       </c>
       <c r="Q33" s="3">
+        <v>1800</v>
+      </c>
+      <c r="R33" s="3">
         <v>1300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-200</v>
-      </c>
-      <c r="AA33" s="3">
-        <v>100</v>
       </c>
       <c r="AB33" s="3">
         <v>100</v>
@@ -2776,8 +2849,11 @@
       <c r="AC33" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD33" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2859,82 +2935,85 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E35" s="3">
         <v>1800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1500</v>
-      </c>
-      <c r="J35" s="3">
-        <v>1600</v>
       </c>
       <c r="K35" s="3">
         <v>1600</v>
       </c>
       <c r="L35" s="3">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="M35" s="3">
         <v>1700</v>
       </c>
       <c r="N35" s="3">
+        <v>1700</v>
+      </c>
+      <c r="O35" s="3">
         <v>1900</v>
-      </c>
-      <c r="O35" s="3">
-        <v>1800</v>
       </c>
       <c r="P35" s="3">
         <v>1800</v>
       </c>
       <c r="Q35" s="3">
+        <v>1800</v>
+      </c>
+      <c r="R35" s="3">
         <v>1300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-200</v>
-      </c>
-      <c r="AA35" s="3">
-        <v>100</v>
       </c>
       <c r="AB35" s="3">
         <v>100</v>
@@ -2942,96 +3021,102 @@
       <c r="AC35" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD35" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3061,8 +3146,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3092,91 +3178,95 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>89700</v>
+      </c>
+      <c r="E41" s="3">
         <v>74700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>41400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>52300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>50400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>61400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>50000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>61500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>82900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>136900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>6900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>8100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>14300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>16200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>17300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>15300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>10000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>5600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>6200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>14300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>6400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>4000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>3300</v>
-      </c>
-      <c r="AA41" s="3">
-        <v>4600</v>
       </c>
       <c r="AB41" s="3">
         <v>4600</v>
       </c>
       <c r="AC41" s="3">
+        <v>4600</v>
+      </c>
+      <c r="AD41" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3208,58 +3298,61 @@
         <v>0</v>
       </c>
       <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>37000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>43900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>57700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>66100</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>107300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>122700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>109000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>97600</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>176900</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>178200</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>185600</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>47200</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>44400</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>35000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>15400</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>26300</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>33800</v>
       </c>
     </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3290,8 +3383,8 @@
       <c r="L43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
+      <c r="M43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N43" s="3">
         <v>0</v>
@@ -3341,8 +3434,11 @@
       <c r="AC43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3358,8 +3454,8 @@
       <c r="G44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H44" s="3">
-        <v>2900</v>
+      <c r="H44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I44" s="3">
         <v>2900</v>
@@ -3374,7 +3470,7 @@
         <v>2900</v>
       </c>
       <c r="M44" s="3">
-        <v>0</v>
+        <v>2900</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -3424,41 +3520,44 @@
       <c r="AC44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>2300</v>
+        <v>2200</v>
       </c>
       <c r="E45" s="3">
         <v>2300</v>
       </c>
       <c r="F45" s="3">
-        <v>2400</v>
+        <v>2300</v>
       </c>
       <c r="G45" s="3">
         <v>2400</v>
       </c>
       <c r="H45" s="3">
+        <v>2400</v>
+      </c>
+      <c r="I45" s="3">
         <v>2200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1600</v>
       </c>
-      <c r="M45" s="3">
-        <v>0</v>
-      </c>
       <c r="N45" s="3">
         <v>0</v>
       </c>
@@ -3507,41 +3606,44 @@
       <c r="AC45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>91900</v>
+      </c>
+      <c r="E46" s="3">
         <v>77000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>43700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>54700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>52800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>66400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>55000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>66300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>87500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>141400</v>
       </c>
-      <c r="M46" s="3">
-        <v>0</v>
-      </c>
       <c r="N46" s="3">
         <v>0</v>
       </c>
@@ -3590,41 +3692,44 @@
       <c r="AC46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>71300</v>
+      </c>
+      <c r="E47" s="3">
         <v>74500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>70000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>86800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>87000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>87900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>88200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>87100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>85600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>88300</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
-      </c>
       <c r="N47" s="3">
         <v>0</v>
       </c>
@@ -3673,91 +3778,97 @@
       <c r="AC47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E48" s="3">
         <v>3200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>5500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4100</v>
-      </c>
-      <c r="O48" s="3">
-        <v>4000</v>
       </c>
       <c r="P48" s="3">
         <v>4000</v>
       </c>
       <c r="Q48" s="3">
+        <v>4000</v>
+      </c>
+      <c r="R48" s="3">
         <v>3800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>7400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>7500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>7600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>8600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>8800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>8900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>9500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>8500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>8600</v>
-      </c>
-      <c r="AA48" s="3">
-        <v>8800</v>
       </c>
       <c r="AB48" s="3">
         <v>8800</v>
       </c>
       <c r="AC48" s="3">
+        <v>8800</v>
+      </c>
+      <c r="AD48" s="3">
         <v>8900</v>
       </c>
     </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3765,37 +3876,37 @@
         <v>18100</v>
       </c>
       <c r="E49" s="3">
-        <v>18200</v>
+        <v>18100</v>
       </c>
       <c r="F49" s="3">
         <v>18200</v>
       </c>
       <c r="G49" s="3">
-        <v>18300</v>
+        <v>18200</v>
       </c>
       <c r="H49" s="3">
         <v>18300</v>
       </c>
       <c r="I49" s="3">
-        <v>18400</v>
+        <v>18300</v>
       </c>
       <c r="J49" s="3">
         <v>18400</v>
       </c>
       <c r="K49" s="3">
-        <v>18500</v>
+        <v>18400</v>
       </c>
       <c r="L49" s="3">
         <v>18500</v>
       </c>
       <c r="M49" s="3">
-        <v>18600</v>
+        <v>18500</v>
       </c>
       <c r="N49" s="3">
         <v>18600</v>
       </c>
       <c r="O49" s="3">
-        <v>18700</v>
+        <v>18600</v>
       </c>
       <c r="P49" s="3">
         <v>18700</v>
@@ -3804,29 +3915,29 @@
         <v>18700</v>
       </c>
       <c r="R49" s="3">
-        <v>18800</v>
+        <v>18700</v>
       </c>
       <c r="S49" s="3">
         <v>18800</v>
       </c>
       <c r="T49" s="3">
-        <v>18900</v>
+        <v>18800</v>
       </c>
       <c r="U49" s="3">
         <v>18900</v>
       </c>
       <c r="V49" s="3">
-        <v>19000</v>
+        <v>18900</v>
       </c>
       <c r="W49" s="3">
         <v>19000</v>
       </c>
       <c r="X49" s="3">
+        <v>19000</v>
+      </c>
+      <c r="Y49" s="3">
         <v>19100</v>
       </c>
-      <c r="Y49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z49" s="3" t="s">
         <v>5</v>
       </c>
@@ -3839,8 +3950,11 @@
       <c r="AC49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3922,8 +4036,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4005,41 +4122,44 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>26800</v>
+      </c>
+      <c r="E52" s="3">
         <v>27100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>24800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>26200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>27800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>27200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>25200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>28000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>27400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>27800</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
-      </c>
       <c r="N52" s="3">
         <v>0</v>
       </c>
@@ -4088,8 +4208,11 @@
       <c r="AC52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4171,91 +4294,97 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>933800</v>
+      </c>
+      <c r="E54" s="3">
         <v>912500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>866800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>878600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>873600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>869500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>843300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>855400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>876900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>932300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>791300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>776400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>766700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>760200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>788100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>790000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>786800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>797300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>850600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>888200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>906400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>642800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>319300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>309700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>305100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>308000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>307700</v>
       </c>
     </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4285,8 +4414,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4316,91 +4446,95 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>749300</v>
+      </c>
+      <c r="E57" s="3">
         <v>730300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>673500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>683800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>689700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>687400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>674400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>709000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>731000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>750800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>7000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>6000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>8200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>7800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>4700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>7600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>5300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>4600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>3900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>4100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>5300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>4700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>4500</v>
       </c>
     </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4408,14 +4542,14 @@
         <v>0</v>
       </c>
       <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
         <v>5400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>4800</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
       <c r="H58" s="3">
         <v>0</v>
       </c>
@@ -4429,11 +4563,11 @@
         <v>0</v>
       </c>
       <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>15000</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
@@ -4482,8 +4616,11 @@
       <c r="AC58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4514,8 +4651,8 @@
       <c r="L59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M59" s="3">
-        <v>0</v>
+      <c r="M59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N59" s="3">
         <v>0</v>
@@ -4565,41 +4702,44 @@
       <c r="AC59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>755700</v>
+      </c>
+      <c r="E60" s="3">
         <v>736200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>681100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>695400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>696700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>694400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>677500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>717000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>739000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>774000</v>
       </c>
-      <c r="M60" s="3">
-        <v>0</v>
-      </c>
       <c r="N60" s="3">
         <v>0</v>
       </c>
@@ -4648,8 +4788,11 @@
       <c r="AC60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4657,32 +4800,32 @@
         <v>54000</v>
       </c>
       <c r="E61" s="3">
+        <v>54000</v>
+      </c>
+      <c r="F61" s="3">
         <v>55000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>54000</v>
-      </c>
-      <c r="G61" s="3">
-        <v>51800</v>
       </c>
       <c r="H61" s="3">
         <v>51800</v>
       </c>
       <c r="I61" s="3">
+        <v>51800</v>
+      </c>
+      <c r="J61" s="3">
         <v>42200</v>
-      </c>
-      <c r="J61" s="3">
-        <v>20000</v>
       </c>
       <c r="K61" s="3">
         <v>20000</v>
       </c>
       <c r="L61" s="3">
+        <v>20000</v>
+      </c>
+      <c r="M61" s="3">
         <v>40000</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -4705,17 +4848,17 @@
         <v>0</v>
       </c>
       <c r="U61" s="3">
+        <v>0</v>
+      </c>
+      <c r="V61" s="3">
         <v>105800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>130000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>129200</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
         <v>0</v>
       </c>
@@ -4731,40 +4874,43 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E62" s="3">
+      <c r="E62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F62" s="3">
         <v>1100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>700</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I62" s="3">
+      <c r="I62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J62" s="3">
         <v>1600</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K62" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M62" s="3">
-        <v>0</v>
+      <c r="M62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N62" s="3">
         <v>0</v>
@@ -4814,8 +4960,11 @@
       <c r="AC62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4897,8 +5046,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4980,8 +5132,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5063,91 +5218,97 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>809700</v>
+      </c>
+      <c r="E66" s="3">
         <v>790200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>737700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>750200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>748500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>746200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>721700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>737000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>759000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>814000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>674200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>661200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>651300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>643900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>667100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>670300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>669200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>682000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>769800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>809000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>829100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>566900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>242100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>233200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>228300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>231700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>231300</v>
       </c>
     </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5177,8 +5338,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5260,8 +5422,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5343,8 +5508,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5426,8 +5594,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5509,91 +5680,97 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>71800</v>
+      </c>
+      <c r="E72" s="3">
         <v>69600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>76800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>75400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>73700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>72700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>71300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>69800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>68200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>66600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>65400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>63700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>61800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>60000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>58200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>56900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>55100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>52800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>50700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>49200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>47300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>46300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>47600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>47100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>47300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>47200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>47000</v>
       </c>
     </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5675,8 +5852,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5758,8 +5938,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5841,91 +6024,97 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>124100</v>
+      </c>
+      <c r="E76" s="3">
         <v>122300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>129100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>128400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>125100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>123300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>121500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>118500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>117900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>118300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>117100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>115200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>115400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>116400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>121000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>119700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>117600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>115300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>80800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>79200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>77200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>75900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>77200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>76500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>76800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>76300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>76400</v>
       </c>
     </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6007,170 +6196,176 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E81" s="3">
         <v>1800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1500</v>
-      </c>
-      <c r="J81" s="3">
-        <v>1600</v>
       </c>
       <c r="K81" s="3">
         <v>1600</v>
       </c>
       <c r="L81" s="3">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="M81" s="3">
         <v>1700</v>
       </c>
       <c r="N81" s="3">
+        <v>1700</v>
+      </c>
+      <c r="O81" s="3">
         <v>1900</v>
-      </c>
-      <c r="O81" s="3">
-        <v>1800</v>
       </c>
       <c r="P81" s="3">
         <v>1800</v>
       </c>
       <c r="Q81" s="3">
+        <v>1800</v>
+      </c>
+      <c r="R81" s="3">
         <v>1300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-200</v>
-      </c>
-      <c r="AA81" s="3">
-        <v>100</v>
       </c>
       <c r="AB81" s="3">
         <v>100</v>
@@ -6178,8 +6373,11 @@
       <c r="AC81" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD81" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6209,8 +6407,9 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6224,26 +6423,26 @@
         <v>100</v>
       </c>
       <c r="G83" s="3">
+        <v>100</v>
+      </c>
+      <c r="H83" s="3">
         <v>200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>-900</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N83" s="3" t="s">
         <v>5</v>
       </c>
@@ -6256,18 +6455,18 @@
       <c r="Q83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R83" s="3">
-        <v>0</v>
-      </c>
-      <c r="S83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T83" s="3">
+      <c r="R83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+      <c r="T83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U83" s="3">
         <v>200</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V83" s="3" t="s">
         <v>5</v>
       </c>
@@ -6277,14 +6476,14 @@
       <c r="X83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Y83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z83" s="3">
         <v>200</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>300</v>
-      </c>
-      <c r="AA83" s="3">
-        <v>200</v>
       </c>
       <c r="AB83" s="3">
         <v>200</v>
@@ -6292,8 +6491,11 @@
       <c r="AC83" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6375,8 +6577,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6458,8 +6663,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6541,8 +6749,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6624,8 +6835,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6707,91 +6921,97 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E89" s="3">
         <v>1900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>4100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>3900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-1300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>3800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>8700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>2400</v>
       </c>
-      <c r="W89" s="3">
-        <v>0</v>
-      </c>
       <c r="X89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y89" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6821,8 +7041,9 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6830,10 +7051,10 @@
         <v>-100</v>
       </c>
       <c r="E91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G91" s="3">
         <v>-100</v>
@@ -6842,10 +7063,10 @@
         <v>-100</v>
       </c>
       <c r="I91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J91" s="3">
         <v>-200</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-100</v>
       </c>
       <c r="K91" s="3">
         <v>-100</v>
@@ -6854,58 +7075,61 @@
         <v>-100</v>
       </c>
       <c r="M91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N91" s="3">
         <v>-500</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-300</v>
       </c>
       <c r="O91" s="3">
         <v>-300</v>
       </c>
       <c r="P91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-400</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>-300</v>
       </c>
       <c r="R91" s="3">
         <v>-300</v>
       </c>
       <c r="S91" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
         <v>-200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-100</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
       <c r="X91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Y91" s="3">
         <v>-100</v>
       </c>
       <c r="Z91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-100</v>
       </c>
-      <c r="AC91" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6987,8 +7211,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7070,91 +7297,97 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-10700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-13900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-14700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>1600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-29200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-26300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-26600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-23800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-17100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-17400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>11200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>23700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-27100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>33400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>5100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-115600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-33300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>13000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-7500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-7000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-4800</v>
       </c>
     </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7184,17 +7417,18 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>0</v>
+      </c>
+      <c r="E96" s="3">
         <v>8800</v>
       </c>
-      <c r="E96" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F96" s="3" t="s">
         <v>5</v>
       </c>
@@ -7216,8 +7450,8 @@
       <c r="L96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -7267,8 +7501,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7350,8 +7587,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7433,8 +7673,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7516,91 +7759,97 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>18100</v>
+      </c>
+      <c r="E100" s="3">
         <v>42100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-10300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>2300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>24800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-14900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-22300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-56600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>137800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>12800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>9300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>7300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-28700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>3300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-13200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-58400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-36600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-22300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>261700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>36400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>9100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>6000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-3900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7631,8 +7880,8 @@
       <c r="L101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -7682,87 +7931,93 @@
       <c r="AC101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E102" s="3">
         <v>33300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-10900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-11000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>11400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-11500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-21400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-54000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>110600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-14200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-14900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-14500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-41900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-19100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>15200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>14300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-76900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-14900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>146100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>10100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>18300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-11000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-6400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-3800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AFBI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AFBI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="92">
   <si>
     <t>AFBI</t>
   </si>
@@ -656,226 +656,232 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>8300</v>
+        <v>8500</v>
       </c>
       <c r="E8" s="3">
         <v>8300</v>
       </c>
       <c r="F8" s="3">
+        <v>8300</v>
+      </c>
+      <c r="G8" s="3">
         <v>7800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>7400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>8000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>7900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>7300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>7400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>7500</v>
-      </c>
-      <c r="M8" s="3">
-        <v>7400</v>
       </c>
       <c r="N8" s="3">
         <v>7400</v>
       </c>
       <c r="O8" s="3">
+        <v>7400</v>
+      </c>
+      <c r="P8" s="3">
         <v>9000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>8200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>7600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>8300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>7400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>7600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>8200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>9200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>8000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>8700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>7300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>6700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3800</v>
-      </c>
-      <c r="AD8" s="3">
-        <v>3600</v>
       </c>
       <c r="AE8" s="3">
         <v>3600</v>
       </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF8" s="3">
+        <v>3600</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -963,46 +969,49 @@
       <c r="AE9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>8300</v>
+        <v>8500</v>
       </c>
       <c r="E10" s="3">
         <v>8300</v>
       </c>
       <c r="F10" s="3">
+        <v>8300</v>
+      </c>
+      <c r="G10" s="3">
         <v>7800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>7400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>8000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>7900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>7300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>7400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>7500</v>
-      </c>
-      <c r="M10" s="3">
-        <v>7400</v>
       </c>
       <c r="N10" s="3">
         <v>7400</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>5</v>
+      <c r="O10" s="3">
+        <v>7400</v>
       </c>
       <c r="P10" s="3" t="s">
         <v>5</v>
@@ -1052,8 +1061,11 @@
       <c r="AE10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1085,8 +1097,9 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1174,8 +1187,11 @@
       <c r="AE12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1263,8 +1279,11 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1301,8 +1320,8 @@
       <c r="N14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1352,13 +1371,16 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E15" s="3">
         <v>200</v>
@@ -1391,7 +1413,7 @@
         <v>200</v>
       </c>
       <c r="O15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="P15" s="3">
         <v>0</v>
@@ -1441,8 +1463,11 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1471,8 +1496,9 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1480,79 +1506,79 @@
         <v>5400</v>
       </c>
       <c r="E17" s="3">
+        <v>5400</v>
+      </c>
+      <c r="F17" s="3">
         <v>5500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>5400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>5800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>5700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>6700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5600</v>
-      </c>
-      <c r="K17" s="3">
-        <v>5400</v>
       </c>
       <c r="L17" s="3">
         <v>5400</v>
       </c>
       <c r="M17" s="3">
+        <v>5400</v>
+      </c>
+      <c r="N17" s="3">
         <v>5300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>700</v>
-      </c>
-      <c r="R17" s="3">
-        <v>800</v>
       </c>
       <c r="S17" s="3">
         <v>800</v>
       </c>
       <c r="T17" s="3">
+        <v>800</v>
+      </c>
+      <c r="U17" s="3">
         <v>1000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1400</v>
-      </c>
-      <c r="Y17" s="3">
-        <v>1500</v>
       </c>
       <c r="Z17" s="3">
         <v>1500</v>
       </c>
       <c r="AA17" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AB17" s="3">
         <v>700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>600</v>
-      </c>
-      <c r="AC17" s="3">
-        <v>500</v>
       </c>
       <c r="AD17" s="3">
         <v>500</v>
@@ -1560,97 +1586,103 @@
       <c r="AE17" s="3">
         <v>500</v>
       </c>
-    </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF17" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E18" s="3">
         <v>2900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>2300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1900</v>
-      </c>
-      <c r="L18" s="3">
-        <v>2100</v>
       </c>
       <c r="M18" s="3">
         <v>2100</v>
       </c>
       <c r="N18" s="3">
+        <v>2100</v>
+      </c>
+      <c r="O18" s="3">
         <v>2200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>7300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>7400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>6900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>7500</v>
-      </c>
-      <c r="S18" s="3">
-        <v>6600</v>
       </c>
       <c r="T18" s="3">
         <v>6600</v>
       </c>
       <c r="U18" s="3">
+        <v>6600</v>
+      </c>
+      <c r="V18" s="3">
         <v>7100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>7800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>6900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>7300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>5800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>5200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>3100</v>
-      </c>
-      <c r="AB18" s="3">
-        <v>3300</v>
       </c>
       <c r="AC18" s="3">
         <v>3300</v>
       </c>
       <c r="AD18" s="3">
-        <v>3100</v>
+        <v>3300</v>
       </c>
       <c r="AE18" s="3">
         <v>3100</v>
       </c>
-    </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF18" s="3">
+        <v>3100</v>
+      </c>
+    </row>
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1682,8 +1714,9 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1696,18 +1729,18 @@
       <c r="F20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I20" s="3">
+      <c r="G20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J20" s="3">
         <v>-100</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K20" s="3" t="s">
         <v>5</v>
       </c>
@@ -1720,98 +1753,101 @@
       <c r="N20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P20" s="3">
         <v>-5100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-4900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-4600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-5200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-4800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-4200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-4100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-5100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-5000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-4800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-4400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-7100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-2800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-3600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-3100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-3000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-2900</v>
       </c>
     </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E21" s="3">
         <v>3100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>3000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2100</v>
-      </c>
-      <c r="L21" s="3">
-        <v>2300</v>
       </c>
       <c r="M21" s="3">
         <v>2300</v>
       </c>
       <c r="N21" s="3">
+        <v>2300</v>
+      </c>
+      <c r="O21" s="3">
         <v>2400</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>5</v>
       </c>
@@ -1830,12 +1866,12 @@
       <c r="U21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V21" s="3">
+      <c r="V21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W21" s="3">
         <v>2900</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X21" s="3" t="s">
         <v>5</v>
       </c>
@@ -1845,14 +1881,14 @@
       <c r="Z21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AA21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB21" s="3">
         <v>600</v>
       </c>
-      <c r="AB21" s="3">
-        <v>0</v>
-      </c>
       <c r="AC21" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AD21" s="3">
         <v>300</v>
@@ -1860,8 +1896,11 @@
       <c r="AE21" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF21" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1898,8 +1937,8 @@
       <c r="N22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -1949,126 +1988,132 @@
       <c r="AE22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E23" s="3">
         <v>2900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1900</v>
-      </c>
-      <c r="L23" s="3">
-        <v>2100</v>
       </c>
       <c r="M23" s="3">
         <v>2100</v>
       </c>
       <c r="N23" s="3">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="O23" s="3">
         <v>2200</v>
       </c>
       <c r="P23" s="3">
+        <v>2200</v>
+      </c>
+      <c r="Q23" s="3">
         <v>2400</v>
-      </c>
-      <c r="Q23" s="3">
-        <v>2300</v>
       </c>
       <c r="R23" s="3">
         <v>2300</v>
       </c>
       <c r="S23" s="3">
+        <v>2300</v>
+      </c>
+      <c r="T23" s="3">
         <v>1800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>3000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>2700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>2400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-300</v>
-      </c>
-      <c r="AC23" s="3">
-        <v>100</v>
       </c>
       <c r="AD23" s="3">
         <v>100</v>
       </c>
       <c r="AE23" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF23" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="E24" s="3">
         <v>700</v>
       </c>
       <c r="F24" s="3">
+        <v>700</v>
+      </c>
+      <c r="G24" s="3">
         <v>600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>300</v>
-      </c>
-      <c r="J24" s="3">
-        <v>400</v>
       </c>
       <c r="K24" s="3">
         <v>400</v>
       </c>
       <c r="L24" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="M24" s="3">
         <v>500</v>
@@ -2080,55 +2125,58 @@
         <v>500</v>
       </c>
       <c r="P24" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="Q24" s="3">
         <v>600</v>
       </c>
       <c r="R24" s="3">
+        <v>600</v>
+      </c>
+      <c r="S24" s="3">
         <v>500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-100</v>
       </c>
-      <c r="AC24" s="3">
-        <v>0</v>
-      </c>
       <c r="AD24" s="3">
         <v>0</v>
       </c>
       <c r="AE24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2216,88 +2264,91 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="E26" s="3">
         <v>2200</v>
       </c>
       <c r="F26" s="3">
+        <v>2200</v>
+      </c>
+      <c r="G26" s="3">
         <v>1800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1500</v>
-      </c>
-      <c r="L26" s="3">
-        <v>1600</v>
       </c>
       <c r="M26" s="3">
         <v>1600</v>
       </c>
       <c r="N26" s="3">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="O26" s="3">
         <v>1700</v>
       </c>
       <c r="P26" s="3">
+        <v>1700</v>
+      </c>
+      <c r="Q26" s="3">
         <v>1900</v>
-      </c>
-      <c r="Q26" s="3">
-        <v>1800</v>
       </c>
       <c r="R26" s="3">
         <v>1800</v>
       </c>
       <c r="S26" s="3">
+        <v>1800</v>
+      </c>
+      <c r="T26" s="3">
         <v>1300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>2100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-200</v>
-      </c>
-      <c r="AC26" s="3">
-        <v>100</v>
       </c>
       <c r="AD26" s="3">
         <v>100</v>
@@ -2305,88 +2356,91 @@
       <c r="AE26" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF26" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="E27" s="3">
         <v>2200</v>
       </c>
       <c r="F27" s="3">
+        <v>2200</v>
+      </c>
+      <c r="G27" s="3">
         <v>1800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1500</v>
-      </c>
-      <c r="L27" s="3">
-        <v>1600</v>
       </c>
       <c r="M27" s="3">
         <v>1600</v>
       </c>
       <c r="N27" s="3">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="O27" s="3">
         <v>1700</v>
       </c>
       <c r="P27" s="3">
+        <v>1700</v>
+      </c>
+      <c r="Q27" s="3">
         <v>1900</v>
-      </c>
-      <c r="Q27" s="3">
-        <v>1800</v>
       </c>
       <c r="R27" s="3">
         <v>1800</v>
       </c>
       <c r="S27" s="3">
+        <v>1800</v>
+      </c>
+      <c r="T27" s="3">
         <v>1300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>2300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>2100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-200</v>
-      </c>
-      <c r="AC27" s="3">
-        <v>100</v>
       </c>
       <c r="AD27" s="3">
         <v>100</v>
@@ -2394,8 +2448,11 @@
       <c r="AE27" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF27" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2483,8 +2540,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2554,8 +2614,8 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>5</v>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>5</v>
@@ -2572,8 +2632,11 @@
       <c r="AE29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2661,8 +2724,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2750,8 +2816,11 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2764,18 +2833,18 @@
       <c r="F32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I32" s="3">
+      <c r="G32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J32" s="3">
         <v>100</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K32" s="3" t="s">
         <v>5</v>
       </c>
@@ -2788,139 +2857,142 @@
       <c r="N32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P32" s="3">
         <v>5100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>4900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>4600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>5200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>4800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>4200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>4100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>5100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>5000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>4800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>4400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>7100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>2800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>3600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>3100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>3000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="E33" s="3">
         <v>2200</v>
       </c>
       <c r="F33" s="3">
+        <v>2200</v>
+      </c>
+      <c r="G33" s="3">
         <v>1800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1500</v>
-      </c>
-      <c r="L33" s="3">
-        <v>1600</v>
       </c>
       <c r="M33" s="3">
         <v>1600</v>
       </c>
       <c r="N33" s="3">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="O33" s="3">
         <v>1700</v>
       </c>
       <c r="P33" s="3">
+        <v>1700</v>
+      </c>
+      <c r="Q33" s="3">
         <v>1900</v>
-      </c>
-      <c r="Q33" s="3">
-        <v>1800</v>
       </c>
       <c r="R33" s="3">
         <v>1800</v>
       </c>
       <c r="S33" s="3">
+        <v>1800</v>
+      </c>
+      <c r="T33" s="3">
         <v>1300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>2100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-200</v>
-      </c>
-      <c r="AC33" s="3">
-        <v>100</v>
       </c>
       <c r="AD33" s="3">
         <v>100</v>
@@ -2928,8 +3000,11 @@
       <c r="AE33" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF33" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3017,88 +3092,91 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="E35" s="3">
         <v>2200</v>
       </c>
       <c r="F35" s="3">
+        <v>2200</v>
+      </c>
+      <c r="G35" s="3">
         <v>1800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1500</v>
-      </c>
-      <c r="L35" s="3">
-        <v>1600</v>
       </c>
       <c r="M35" s="3">
         <v>1600</v>
       </c>
       <c r="N35" s="3">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="O35" s="3">
         <v>1700</v>
       </c>
       <c r="P35" s="3">
+        <v>1700</v>
+      </c>
+      <c r="Q35" s="3">
         <v>1900</v>
-      </c>
-      <c r="Q35" s="3">
-        <v>1800</v>
       </c>
       <c r="R35" s="3">
         <v>1800</v>
       </c>
       <c r="S35" s="3">
+        <v>1800</v>
+      </c>
+      <c r="T35" s="3">
         <v>1300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>2100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-200</v>
-      </c>
-      <c r="AC35" s="3">
-        <v>100</v>
       </c>
       <c r="AD35" s="3">
         <v>100</v>
@@ -3106,102 +3184,108 @@
       <c r="AE35" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF35" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3233,8 +3317,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3266,97 +3351,101 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>53900</v>
+      </c>
+      <c r="E41" s="3">
         <v>84800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>89700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>74700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>41400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>52300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>50400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>61400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>50000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>61500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>82900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>136900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>6900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>8100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>14300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>16200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>17300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>15300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>10000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>5600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>6200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>14300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>6400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>4000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>3300</v>
-      </c>
-      <c r="AC41" s="3">
-        <v>4600</v>
       </c>
       <c r="AD41" s="3">
         <v>4600</v>
       </c>
       <c r="AE41" s="3">
+        <v>4600</v>
+      </c>
+      <c r="AF41" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3394,58 +3483,61 @@
         <v>0</v>
       </c>
       <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
         <v>37000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>43900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>57700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>66100</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>107300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>122700</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>109000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>97600</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>176900</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>178200</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>185600</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>47200</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>44400</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>35000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>15400</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>26300</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>33800</v>
       </c>
     </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3482,8 +3574,8 @@
       <c r="N43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
+      <c r="O43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P43" s="3">
         <v>0</v>
@@ -3533,8 +3625,11 @@
       <c r="AE43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3556,8 +3651,8 @@
       <c r="I44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J44" s="3">
-        <v>2900</v>
+      <c r="J44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K44" s="3">
         <v>2900</v>
@@ -3572,7 +3667,7 @@
         <v>2900</v>
       </c>
       <c r="O44" s="3">
-        <v>0</v>
+        <v>2900</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -3622,47 +3717,50 @@
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>2200</v>
+        <v>2300</v>
       </c>
       <c r="E45" s="3">
         <v>2200</v>
       </c>
       <c r="F45" s="3">
-        <v>2300</v>
+        <v>2200</v>
       </c>
       <c r="G45" s="3">
         <v>2300</v>
       </c>
       <c r="H45" s="3">
-        <v>2400</v>
+        <v>2300</v>
       </c>
       <c r="I45" s="3">
         <v>2400</v>
       </c>
       <c r="J45" s="3">
+        <v>2400</v>
+      </c>
+      <c r="K45" s="3">
         <v>2200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1600</v>
       </c>
-      <c r="O45" s="3">
-        <v>0</v>
-      </c>
       <c r="P45" s="3">
         <v>0</v>
       </c>
@@ -3711,47 +3809,50 @@
       <c r="AE45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>56200</v>
+      </c>
+      <c r="E46" s="3">
         <v>87000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>91900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>77000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>43700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>54700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>52800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>66400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>55000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>66300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>87500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>141400</v>
       </c>
-      <c r="O46" s="3">
-        <v>0</v>
-      </c>
       <c r="P46" s="3">
         <v>0</v>
       </c>
@@ -3800,47 +3901,50 @@
       <c r="AE46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>45000</v>
+      </c>
+      <c r="E47" s="3">
         <v>70100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>71300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>74500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>70000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>86800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>87000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>87900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>88200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>87100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>85600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>88300</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
       <c r="P47" s="3">
         <v>0</v>
       </c>
@@ -3889,97 +3993,103 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E48" s="3">
         <v>3000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4100</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>4000</v>
       </c>
       <c r="R48" s="3">
         <v>4000</v>
       </c>
       <c r="S48" s="3">
+        <v>4000</v>
+      </c>
+      <c r="T48" s="3">
         <v>3800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>7400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>7500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>7600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>8600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>8800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>8900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>9500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>8500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>8600</v>
-      </c>
-      <c r="AC48" s="3">
-        <v>8800</v>
       </c>
       <c r="AD48" s="3">
         <v>8800</v>
       </c>
       <c r="AE48" s="3">
+        <v>8800</v>
+      </c>
+      <c r="AF48" s="3">
         <v>8900</v>
       </c>
     </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3987,43 +4097,43 @@
         <v>18000</v>
       </c>
       <c r="E49" s="3">
-        <v>18100</v>
+        <v>18000</v>
       </c>
       <c r="F49" s="3">
         <v>18100</v>
       </c>
       <c r="G49" s="3">
-        <v>18200</v>
+        <v>18100</v>
       </c>
       <c r="H49" s="3">
         <v>18200</v>
       </c>
       <c r="I49" s="3">
-        <v>18300</v>
+        <v>18200</v>
       </c>
       <c r="J49" s="3">
         <v>18300</v>
       </c>
       <c r="K49" s="3">
-        <v>18400</v>
+        <v>18300</v>
       </c>
       <c r="L49" s="3">
         <v>18400</v>
       </c>
       <c r="M49" s="3">
-        <v>18500</v>
+        <v>18400</v>
       </c>
       <c r="N49" s="3">
         <v>18500</v>
       </c>
       <c r="O49" s="3">
-        <v>18600</v>
+        <v>18500</v>
       </c>
       <c r="P49" s="3">
         <v>18600</v>
       </c>
       <c r="Q49" s="3">
-        <v>18700</v>
+        <v>18600</v>
       </c>
       <c r="R49" s="3">
         <v>18700</v>
@@ -4032,29 +4142,29 @@
         <v>18700</v>
       </c>
       <c r="T49" s="3">
-        <v>18800</v>
+        <v>18700</v>
       </c>
       <c r="U49" s="3">
         <v>18800</v>
       </c>
       <c r="V49" s="3">
-        <v>18900</v>
+        <v>18800</v>
       </c>
       <c r="W49" s="3">
         <v>18900</v>
       </c>
       <c r="X49" s="3">
-        <v>19000</v>
+        <v>18900</v>
       </c>
       <c r="Y49" s="3">
         <v>19000</v>
       </c>
       <c r="Z49" s="3">
+        <v>19000</v>
+      </c>
+      <c r="AA49" s="3">
         <v>19100</v>
       </c>
-      <c r="AA49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB49" s="3" t="s">
         <v>5</v>
       </c>
@@ -4067,8 +4177,11 @@
       <c r="AE49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4156,8 +4269,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4245,47 +4361,50 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>25300</v>
+      </c>
+      <c r="E52" s="3">
         <v>26100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>26800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>27100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>24800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>26200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>27800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>27200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>25200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>28000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>27400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>27800</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
-      </c>
       <c r="P52" s="3">
         <v>0</v>
       </c>
@@ -4334,8 +4453,11 @@
       <c r="AE52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4423,97 +4545,103 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>881700</v>
+      </c>
+      <c r="E54" s="3">
         <v>925200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>933800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>912500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>866800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>878600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>873600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>869500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>843300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>855400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>876900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>932300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>791300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>776400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>766700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>760200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>788100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>790000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>786800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>797300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>850600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>888200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>906400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>642800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>319300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>309700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>305100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>308000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>307700</v>
       </c>
     </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4545,8 +4673,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4578,117 +4707,121 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>695000</v>
+      </c>
+      <c r="E57" s="3">
         <v>739400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>749300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>730300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>673500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>683800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>689700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>687400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>674400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>709000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>731000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>750800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>7000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>5100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>5800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>6000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>8200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>7800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>4700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>7600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>5300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>4600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>3900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>4100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>5300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>4700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>4500</v>
       </c>
     </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E58" s="3">
         <v>20000</v>
       </c>
-      <c r="E58" s="3">
-        <v>0</v>
-      </c>
       <c r="F58" s="3">
         <v>0</v>
       </c>
       <c r="G58" s="3">
-        <v>5400</v>
+        <v>0</v>
       </c>
       <c r="H58" s="3">
         <v>4800</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>4800</v>
       </c>
       <c r="J58" s="3">
         <v>0</v>
@@ -4703,11 +4836,11 @@
         <v>0</v>
       </c>
       <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
         <v>15000</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
         <v>0</v>
       </c>
@@ -4756,8 +4889,11 @@
       <c r="AE58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4794,8 +4930,8 @@
       <c r="N59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O59" s="3">
-        <v>0</v>
+      <c r="O59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P59" s="3">
         <v>0</v>
@@ -4845,47 +4981,50 @@
       <c r="AE59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>708900</v>
+      </c>
+      <c r="E60" s="3">
         <v>765800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>755700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>736200</v>
       </c>
-      <c r="G60" s="3">
-        <v>681100</v>
-      </c>
       <c r="H60" s="3">
+        <v>680500</v>
+      </c>
+      <c r="I60" s="3">
         <v>695400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>696700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>694400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>677500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>717000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>739000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>774000</v>
       </c>
-      <c r="O60" s="3">
-        <v>0</v>
-      </c>
       <c r="P60" s="3">
         <v>0</v>
       </c>
@@ -4934,47 +5073,50 @@
       <c r="AE60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>44300</v>
+      </c>
+      <c r="E61" s="3">
         <v>34000</v>
-      </c>
-      <c r="E61" s="3">
-        <v>54000</v>
       </c>
       <c r="F61" s="3">
         <v>54000</v>
       </c>
       <c r="G61" s="3">
-        <v>55000</v>
+        <v>54000</v>
       </c>
       <c r="H61" s="3">
+        <v>55600</v>
+      </c>
+      <c r="I61" s="3">
         <v>54000</v>
-      </c>
-      <c r="I61" s="3">
-        <v>51800</v>
       </c>
       <c r="J61" s="3">
         <v>51800</v>
       </c>
       <c r="K61" s="3">
+        <v>51800</v>
+      </c>
+      <c r="L61" s="3">
         <v>42200</v>
-      </c>
-      <c r="L61" s="3">
-        <v>20000</v>
       </c>
       <c r="M61" s="3">
         <v>20000</v>
       </c>
       <c r="N61" s="3">
+        <v>20000</v>
+      </c>
+      <c r="O61" s="3">
         <v>40000</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -4997,17 +5139,17 @@
         <v>0</v>
       </c>
       <c r="W61" s="3">
+        <v>0</v>
+      </c>
+      <c r="X61" s="3">
         <v>105800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>130000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>129200</v>
       </c>
-      <c r="Z61" s="3">
-        <v>0</v>
-      </c>
       <c r="AA61" s="3">
         <v>0</v>
       </c>
@@ -5023,13 +5165,16 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>5</v>
+      <c r="D62" s="3">
+        <v>900</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>5</v>
@@ -5037,32 +5182,32 @@
       <c r="F62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G62" s="3">
+      <c r="G62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H62" s="3">
         <v>1100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>700</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L62" s="3">
         <v>1600</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M62" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O62" s="3">
-        <v>0</v>
+      <c r="O62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P62" s="3">
         <v>0</v>
@@ -5112,8 +5257,11 @@
       <c r="AE62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5201,8 +5349,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5290,8 +5441,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5379,97 +5533,103 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>754700</v>
+      </c>
+      <c r="E66" s="3">
         <v>799800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>809700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>790200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>737700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>750200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>748500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>746200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>721700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>737000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>759000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>814000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>674200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>661200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>651300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>643900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>667100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>670300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>669200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>682000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>769800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>809000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>829100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>566900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>242100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>233200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>228300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>231700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>231300</v>
       </c>
     </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5501,8 +5661,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5590,8 +5751,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5679,8 +5843,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5768,8 +5935,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5857,97 +6027,103 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>76100</v>
+      </c>
+      <c r="E72" s="3">
         <v>74000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>71800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>69600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>76800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>75400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>73700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>72700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>71300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>69800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>68200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>66600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>65400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>63700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>61800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>60000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>58200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>56900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>55100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>52800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>50700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>49200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>47300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>46300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>47600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>47100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>47300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>47200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>47000</v>
       </c>
     </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6035,8 +6211,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6124,8 +6303,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6213,97 +6395,103 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>127000</v>
+      </c>
+      <c r="E76" s="3">
         <v>125400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>124100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>122300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>129100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>128400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>125100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>123300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>121500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>118500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>117900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>118300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>117100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>115200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>115400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>116400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>121000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>119700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>117600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>115300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>80800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>79200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>77200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>75900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>77200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>76500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>76800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>76300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>76400</v>
       </c>
     </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6391,182 +6579,188 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="E81" s="3">
         <v>2200</v>
       </c>
       <c r="F81" s="3">
+        <v>2200</v>
+      </c>
+      <c r="G81" s="3">
         <v>1800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1500</v>
-      </c>
-      <c r="L81" s="3">
-        <v>1600</v>
       </c>
       <c r="M81" s="3">
         <v>1600</v>
       </c>
       <c r="N81" s="3">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="O81" s="3">
         <v>1700</v>
       </c>
       <c r="P81" s="3">
+        <v>1700</v>
+      </c>
+      <c r="Q81" s="3">
         <v>1900</v>
-      </c>
-      <c r="Q81" s="3">
-        <v>1800</v>
       </c>
       <c r="R81" s="3">
         <v>1800</v>
       </c>
       <c r="S81" s="3">
+        <v>1800</v>
+      </c>
+      <c r="T81" s="3">
         <v>1300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>2100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-1300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-200</v>
-      </c>
-      <c r="AC81" s="3">
-        <v>100</v>
       </c>
       <c r="AD81" s="3">
         <v>100</v>
@@ -6574,8 +6768,11 @@
       <c r="AE81" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF81" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6607,13 +6804,14 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E83" s="3">
         <v>100</v>
@@ -6628,26 +6826,26 @@
         <v>100</v>
       </c>
       <c r="I83" s="3">
+        <v>100</v>
+      </c>
+      <c r="J83" s="3">
         <v>200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>-900</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P83" s="3" t="s">
         <v>5</v>
       </c>
@@ -6660,18 +6858,18 @@
       <c r="S83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T83" s="3">
-        <v>0</v>
-      </c>
-      <c r="U83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V83" s="3">
+      <c r="T83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U83" s="3">
+        <v>0</v>
+      </c>
+      <c r="V83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W83" s="3">
         <v>200</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X83" s="3" t="s">
         <v>5</v>
       </c>
@@ -6681,14 +6879,14 @@
       <c r="Z83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AA83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB83" s="3">
         <v>200</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>300</v>
-      </c>
-      <c r="AC83" s="3">
-        <v>200</v>
       </c>
       <c r="AD83" s="3">
         <v>200</v>
@@ -6696,8 +6894,11 @@
       <c r="AE83" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6785,8 +6986,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6874,8 +7078,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6963,8 +7170,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7052,8 +7262,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7141,97 +7354,103 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E89" s="3">
         <v>3700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>4100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>2000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>3900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-1300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>3800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>8700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>2400</v>
       </c>
-      <c r="Y89" s="3">
-        <v>0</v>
-      </c>
       <c r="Z89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA89" s="3">
         <v>-2900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7263,8 +7482,9 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7278,10 +7498,10 @@
         <v>-100</v>
       </c>
       <c r="G91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I91" s="3">
         <v>-100</v>
@@ -7290,10 +7510,10 @@
         <v>-100</v>
       </c>
       <c r="K91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L91" s="3">
         <v>-200</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-100</v>
       </c>
       <c r="M91" s="3">
         <v>-100</v>
@@ -7302,58 +7522,61 @@
         <v>-100</v>
       </c>
       <c r="O91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P91" s="3">
         <v>-500</v>
-      </c>
-      <c r="P91" s="3">
-        <v>-300</v>
       </c>
       <c r="Q91" s="3">
         <v>-300</v>
       </c>
       <c r="R91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="S91" s="3">
         <v>-400</v>
-      </c>
-      <c r="S91" s="3">
-        <v>-300</v>
       </c>
       <c r="T91" s="3">
         <v>-300</v>
       </c>
       <c r="U91" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3">
         <v>-200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-100</v>
       </c>
-      <c r="Y91" s="3">
-        <v>0</v>
-      </c>
       <c r="Z91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AA91" s="3">
         <v>-100</v>
       </c>
       <c r="AB91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-100</v>
       </c>
-      <c r="AE91" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7441,8 +7664,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7530,97 +7756,103 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E94" s="3">
         <v>3400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-6900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-10700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-13900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-14700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>1600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-29200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-26300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-26600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-23800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-17100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-17400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>11200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>23700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-27100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>33400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>5100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-115600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-33300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>13000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-7500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-7000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-4800</v>
       </c>
     </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7652,8 +7884,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7664,11 +7897,11 @@
         <v>0</v>
       </c>
       <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
         <v>8800</v>
       </c>
-      <c r="G96" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H96" s="3" t="s">
         <v>5</v>
       </c>
@@ -7690,8 +7923,8 @@
       <c r="N96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -7741,8 +7974,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7830,8 +8066,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7919,8 +8158,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8008,97 +8250,103 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-46200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-11900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>18100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>42100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-10300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>2300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>24800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-14900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-22300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-56600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>137800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>12800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>9300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>7300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-28700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>3300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-13200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-58400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-36600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-22300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>261700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>36400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>9100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>6000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-3900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8135,8 +8383,8 @@
       <c r="N101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -8186,93 +8434,99 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-31000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-4800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>15000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>33300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-10900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-11000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>11400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-11500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-21400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-54000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>110600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-14200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-14900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-14500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-41900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-19100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>15200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>14300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-76900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-1300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-14900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>146100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>10100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>18300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-11000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-6400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-3800</v>
       </c>
     </row>
